--- a/BASE_ONBOARDING_ESCUELA_COMERCIAL (4) (1).xlsx
+++ b/BASE_ONBOARDING_ESCUELA_COMERCIAL (4) (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cuneduco-my.sharepoint.com/personal/yeison_oyolat_cun_edu_co/Documents/Documentos/Margaret/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="269" documentId="114_{60450292-222E-4A60-9E8E-D1FE92304973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F48050D-0F60-47D7-9A67-AE0954166FED}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="114_{60450292-222E-4A60-9E8E-D1FE92304973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9109FAC-8B1A-432E-ABD0-9D43FDB307B2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="4185" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId6"/>
-    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
+    <pivotCache cacheId="1" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -962,7 +962,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1028,6 +1028,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1035,7 +1059,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1202,9 +1226,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1246,6 +1267,33 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="22" fillId="8" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2223,6 +2271,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="YEISON HERNAN OLAYA TRIVIÑO" refreshedDate="46230.365198726853" createdVersion="5" refreshedVersion="8" minRefreshableVersion="3" recordCount="13" xr:uid="{FF4D2FCE-CC14-4EEB-8DB7-EBB1E93BE88C}">
   <cacheSource type="worksheet">
@@ -3165,142 +3217,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C9E3E94-D17B-48CC-95A0-84A7D7C5E77E}" name="PT_OJT_Campana" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A21:C24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="7"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cantidad  " fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91F26FD7-15A9-43D0-BB54-C5374415611B}" name="PT_Onboarding_Cargo" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="K5:N8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="18">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="49" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item m="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="16"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Cantidad " fld="4" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEE47274-C06C-4A82-AD90-268267555A91}" name="PT_Onboarding_Notas" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AEE47274-C06C-4A82-AD90-268267555A91}" name="PT_Onboarding_Notas" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G5:H8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -3383,8 +3300,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1DF9DE30-007D-4EE5-91AF-9043DF260E0A}" name="PT_Onboarding_Campana" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1DF9DE30-007D-4EE5-91AF-9043DF260E0A}" name="PT_Onboarding_Campana" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A5:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -3462,8 +3379,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9257CECC-D623-4197-834C-86B55F3CE2FD}" name="PT_OJT_Notas" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9257CECC-D623-4197-834C-86B55F3CE2FD}" name="PT_OJT_Notas" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="G21:H23" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -3496,6 +3413,141 @@
   </colItems>
   <dataFields count="1">
     <dataField name="Nota Promedio " fld="6" subtotal="average" baseField="0" baseItem="0" numFmtId="167"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1C9E3E94-D17B-48CC-95A0-84A7D7C5E77E}" name="PT_OJT_Campana" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A21:C24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cantidad  " fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{91F26FD7-15A9-43D0-BB54-C5374415611B}" name="PT_Onboarding_Cargo" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K5:N8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="18">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="49" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item m="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="16"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Cantidad " fld="4" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -6589,17 +6641,14 @@
       </c>
     </row>
     <row r="48" spans="1:20" ht="15" customHeight="1">
-      <c r="A48" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A48" s="18"/>
       <c r="B48" s="19"/>
       <c r="C48" s="20"/>
       <c r="D48" s="19"/>
       <c r="E48" s="22"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="30"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="75"/>
       <c r="I48" s="19"/>
       <c r="J48" s="25"/>
       <c r="K48" s="25"/>
@@ -6607,14 +6656,8 @@
       <c r="M48" s="25"/>
       <c r="N48" s="25"/>
       <c r="O48" s="25"/>
-      <c r="P48" s="31" t="str">
-        <f>IF(F48="","",IF(COUNTIF(J48:O48,"D")&gt;0,"",(IF(ISNUMBER(J48),J48,0)*Parametros!$K$4+IF(ISNUMBER(K48),K48,0)*Parametros!$K$5+IF(ISNUMBER(M48),M48,0)*Parametros!$K$6+IF(ISNUMBER(N48),N48,0)*Parametros!$K$7+IF(ISNUMBER(O48),O48,0)*Parametros!$K$8)/Parametros!$B$2))</f>
-        <v/>
-      </c>
-      <c r="Q48" s="3" t="str">
-        <f>IF(F48="","",IF(COUNTIF(J48:O48,"D")&gt;0,"Desiste",IF(IFERROR(P48,0)&gt;=Parametros!$B$1,"Aprueba","No aprueba")))</f>
-        <v/>
-      </c>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="3"/>
       <c r="R48" s="19"/>
       <c r="T48" t="str">
         <f>IF($Q48="Aprueba",COUNTIF($Q$2:$Q48,"Aprueba"),"")</f>
@@ -6622,10 +6665,7 @@
       </c>
     </row>
     <row r="49" spans="1:20" ht="15" customHeight="1">
-      <c r="A49" s="18" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="A49" s="18"/>
       <c r="B49" s="19"/>
       <c r="C49" s="20"/>
       <c r="D49" s="19"/>
@@ -6640,14 +6680,8 @@
       <c r="M49" s="25"/>
       <c r="N49" s="25"/>
       <c r="O49" s="25"/>
-      <c r="P49" s="31" t="str">
-        <f>IF(F49="","",IF(COUNTIF(J49:O49,"D")&gt;0,"",(IF(ISNUMBER(J49),J49,0)*Parametros!$K$4+IF(ISNUMBER(K49),K49,0)*Parametros!$K$5+IF(ISNUMBER(M49),M49,0)*Parametros!$K$6+IF(ISNUMBER(N49),N49,0)*Parametros!$K$7+IF(ISNUMBER(O49),O49,0)*Parametros!$K$8)/Parametros!$B$2))</f>
-        <v/>
-      </c>
-      <c r="Q49" s="3" t="str">
-        <f>IF(F49="","",IF(COUNTIF(J49:O49,"D")&gt;0,"Desiste",IF(IFERROR(P49,0)&gt;=Parametros!$B$1,"Aprueba","No aprueba")))</f>
-        <v/>
-      </c>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="3"/>
       <c r="R49" s="19"/>
       <c r="T49" t="str">
         <f>IF($Q49="Aprueba",COUNTIF($Q$2:$Q49,"Aprueba"),"")</f>
@@ -14423,7 +14457,7 @@
     <col min="2" max="2" width="17.140625" style="64" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="64" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" style="64" customWidth="1"/>
-    <col min="5" max="5" width="22.85546875" style="88" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" style="87" customWidth="1"/>
     <col min="6" max="6" width="18.28515625" style="64" customWidth="1"/>
     <col min="7" max="7" width="16" style="64" customWidth="1"/>
     <col min="8" max="9" width="13.7109375" style="64" customWidth="1"/>
@@ -14471,23 +14505,23 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A2" s="92">
+      <c r="A2" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(1,Registro!$T$2:$T$100,0))="","", 1),"")</f>
         <v>1</v>
       </c>
-      <c r="B2" s="93">
+      <c r="B2" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(1,Registro!$T$2:$T$100,0)),"")</f>
         <v>1193156026</v>
       </c>
-      <c r="C2" s="93" t="str">
+      <c r="C2" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(1,Registro!$T$2:$T$100,0)),"")</f>
         <v>Sara Isabel Molina Sánchez</v>
       </c>
-      <c r="D2" s="93" t="str">
+      <c r="D2" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(1,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E2" s="95">
+      <c r="E2" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(1,Registro!$T$2:$T$100,0)),"")</f>
         <v>72</v>
       </c>
@@ -14496,92 +14530,92 @@
       </c>
       <c r="G2" s="68"/>
       <c r="H2" s="69"/>
-      <c r="I2" s="89"/>
+      <c r="I2" s="88"/>
       <c r="J2" s="69"/>
-      <c r="K2" s="66"/>
+      <c r="K2" s="99"/>
       <c r="L2" s="67"/>
     </row>
     <row r="3" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A3" s="92"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="95"/>
+      <c r="A3" s="91"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="92"/>
+      <c r="E3" s="94"/>
       <c r="F3" s="66">
         <v>2</v>
       </c>
       <c r="G3" s="68"/>
       <c r="H3" s="69"/>
-      <c r="I3" s="90"/>
-      <c r="K3" s="66"/>
+      <c r="I3" s="89"/>
+      <c r="K3" s="100"/>
       <c r="L3" s="67"/>
     </row>
     <row r="4" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A4" s="92"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="95"/>
+      <c r="A4" s="91"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="94"/>
       <c r="F4" s="66">
         <v>3</v>
       </c>
       <c r="G4" s="68"/>
       <c r="H4" s="69"/>
-      <c r="I4" s="90"/>
+      <c r="I4" s="89"/>
       <c r="J4" s="69"/>
-      <c r="K4" s="66"/>
+      <c r="K4" s="100"/>
       <c r="L4" s="67"/>
     </row>
     <row r="5" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A5" s="92"/>
-      <c r="B5" s="94"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="95"/>
+      <c r="A5" s="91"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
+      <c r="E5" s="94"/>
       <c r="F5" s="66">
         <v>4</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="69"/>
-      <c r="I5" s="90"/>
+      <c r="I5" s="89"/>
       <c r="J5" s="69"/>
-      <c r="K5" s="66"/>
+      <c r="K5" s="100"/>
       <c r="L5" s="67"/>
     </row>
     <row r="6" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A6" s="92"/>
-      <c r="B6" s="94"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="95"/>
+      <c r="A6" s="91"/>
+      <c r="B6" s="93"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="92"/>
+      <c r="E6" s="94"/>
       <c r="F6" s="66">
         <v>5</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="69"/>
-      <c r="I6" s="90"/>
+      <c r="I6" s="89"/>
       <c r="J6" s="69"/>
-      <c r="K6" s="66"/>
+      <c r="K6" s="101"/>
       <c r="L6" s="67"/>
     </row>
     <row r="7" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A7" s="96">
+      <c r="A7" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(2,Registro!$T$2:$T$100,0))="","", 2),"")</f>
         <v>2</v>
       </c>
-      <c r="B7" s="97">
+      <c r="B7" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(2,Registro!$T$2:$T$100,0)),"")</f>
         <v>1016001652</v>
       </c>
-      <c r="C7" s="97" t="str">
+      <c r="C7" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(2,Registro!$T$2:$T$100,0)),"")</f>
         <v>Helen Sofia Calderon Camelo</v>
       </c>
-      <c r="D7" s="97" t="str">
+      <c r="D7" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(2,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E7" s="99">
+      <c r="E7" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(2,Registro!$T$2:$T$100,0)),"")</f>
         <v>70</v>
       </c>
@@ -14590,93 +14624,93 @@
       </c>
       <c r="G7" s="72"/>
       <c r="H7" s="73"/>
-      <c r="I7" s="91"/>
+      <c r="I7" s="90"/>
       <c r="J7" s="73"/>
-      <c r="K7" s="84"/>
+      <c r="K7" s="102"/>
       <c r="L7" s="71"/>
     </row>
     <row r="8" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A8" s="96"/>
-      <c r="B8" s="98"/>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="99"/>
+      <c r="A8" s="95"/>
+      <c r="B8" s="97"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="98"/>
       <c r="F8" s="70">
         <v>2</v>
       </c>
       <c r="G8" s="72"/>
       <c r="H8" s="73"/>
-      <c r="I8" s="91"/>
+      <c r="I8" s="90"/>
       <c r="J8" s="73"/>
-      <c r="K8" s="84"/>
+      <c r="K8" s="103"/>
       <c r="L8" s="71"/>
     </row>
     <row r="9" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A9" s="96"/>
-      <c r="B9" s="98"/>
-      <c r="C9" s="97"/>
-      <c r="D9" s="97"/>
-      <c r="E9" s="99"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="97"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="98"/>
       <c r="F9" s="70">
         <v>3</v>
       </c>
       <c r="G9" s="72"/>
       <c r="H9" s="73"/>
-      <c r="I9" s="91"/>
+      <c r="I9" s="90"/>
       <c r="J9" s="73"/>
-      <c r="K9" s="84"/>
+      <c r="K9" s="103"/>
       <c r="L9" s="71"/>
     </row>
     <row r="10" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A10" s="96"/>
-      <c r="B10" s="98"/>
-      <c r="C10" s="97"/>
-      <c r="D10" s="97"/>
-      <c r="E10" s="99"/>
+      <c r="A10" s="95"/>
+      <c r="B10" s="97"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="98"/>
       <c r="F10" s="70">
         <v>4</v>
       </c>
       <c r="G10" s="72"/>
       <c r="H10" s="73"/>
-      <c r="I10" s="91"/>
+      <c r="I10" s="90"/>
       <c r="J10" s="73"/>
-      <c r="K10" s="84"/>
+      <c r="K10" s="103"/>
       <c r="L10" s="71"/>
     </row>
     <row r="11" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A11" s="96"/>
-      <c r="B11" s="98"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="99"/>
+      <c r="A11" s="95"/>
+      <c r="B11" s="97"/>
+      <c r="C11" s="96"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="98"/>
       <c r="F11" s="70">
         <v>5</v>
       </c>
       <c r="G11" s="72"/>
       <c r="H11" s="73"/>
-      <c r="I11" s="91"/>
+      <c r="I11" s="90"/>
       <c r="J11" s="73"/>
-      <c r="K11" s="84"/>
+      <c r="K11" s="104"/>
       <c r="L11" s="71"/>
     </row>
     <row r="12" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A12" s="92">
+      <c r="A12" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(3,Registro!$T$2:$T$100,0))="","", 3),"")</f>
         <v>3</v>
       </c>
-      <c r="B12" s="93">
+      <c r="B12" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(3,Registro!$T$2:$T$100,0)),"")</f>
         <v>1001314657</v>
       </c>
-      <c r="C12" s="93" t="str">
+      <c r="C12" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(3,Registro!$T$2:$T$100,0)),"")</f>
         <v>Thomas Bernardo Fernandez Laverde</v>
       </c>
-      <c r="D12" s="93" t="str">
+      <c r="D12" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(3,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E12" s="95">
+      <c r="E12" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(3,Registro!$T$2:$T$100,0)),"")</f>
         <v>72</v>
       </c>
@@ -14685,93 +14719,93 @@
       </c>
       <c r="G12" s="68"/>
       <c r="H12" s="69"/>
-      <c r="I12" s="90"/>
+      <c r="I12" s="89"/>
       <c r="J12" s="69"/>
-      <c r="K12" s="66"/>
+      <c r="K12" s="99"/>
       <c r="L12" s="67"/>
     </row>
     <row r="13" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A13" s="92"/>
-      <c r="B13" s="94"/>
-      <c r="C13" s="93"/>
-      <c r="D13" s="93"/>
-      <c r="E13" s="95"/>
+      <c r="A13" s="91"/>
+      <c r="B13" s="93"/>
+      <c r="C13" s="92"/>
+      <c r="D13" s="92"/>
+      <c r="E13" s="94"/>
       <c r="F13" s="66">
         <v>2</v>
       </c>
       <c r="G13" s="68"/>
       <c r="H13" s="69"/>
-      <c r="I13" s="90"/>
+      <c r="I13" s="89"/>
       <c r="J13" s="69"/>
-      <c r="K13" s="66"/>
+      <c r="K13" s="100"/>
       <c r="L13" s="67"/>
     </row>
     <row r="14" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A14" s="92"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="95"/>
+      <c r="A14" s="91"/>
+      <c r="B14" s="93"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="94"/>
       <c r="F14" s="66">
         <v>3</v>
       </c>
       <c r="G14" s="68"/>
       <c r="H14" s="69"/>
-      <c r="I14" s="90"/>
+      <c r="I14" s="89"/>
       <c r="J14" s="69"/>
-      <c r="K14" s="66"/>
+      <c r="K14" s="100"/>
       <c r="L14" s="67"/>
     </row>
     <row r="15" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A15" s="92"/>
-      <c r="B15" s="94"/>
-      <c r="C15" s="93"/>
-      <c r="D15" s="93"/>
-      <c r="E15" s="95"/>
+      <c r="A15" s="91"/>
+      <c r="B15" s="93"/>
+      <c r="C15" s="92"/>
+      <c r="D15" s="92"/>
+      <c r="E15" s="94"/>
       <c r="F15" s="66">
         <v>4</v>
       </c>
       <c r="G15" s="68"/>
       <c r="H15" s="69"/>
-      <c r="I15" s="90"/>
+      <c r="I15" s="89"/>
       <c r="J15" s="69"/>
-      <c r="K15" s="66"/>
+      <c r="K15" s="100"/>
       <c r="L15" s="67"/>
     </row>
     <row r="16" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A16" s="92"/>
-      <c r="B16" s="94"/>
-      <c r="C16" s="93"/>
-      <c r="D16" s="93"/>
-      <c r="E16" s="95"/>
+      <c r="A16" s="91"/>
+      <c r="B16" s="93"/>
+      <c r="C16" s="92"/>
+      <c r="D16" s="92"/>
+      <c r="E16" s="94"/>
       <c r="F16" s="66">
         <v>5</v>
       </c>
       <c r="G16" s="68"/>
       <c r="H16" s="69"/>
-      <c r="I16" s="90"/>
+      <c r="I16" s="89"/>
       <c r="J16" s="69"/>
-      <c r="K16" s="66"/>
+      <c r="K16" s="101"/>
       <c r="L16" s="67"/>
     </row>
     <row r="17" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A17" s="96">
+      <c r="A17" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(4,Registro!$T$2:$T$100,0))="","", 4),"")</f>
         <v>4</v>
       </c>
-      <c r="B17" s="97">
+      <c r="B17" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(4,Registro!$T$2:$T$100,0)),"")</f>
         <v>1033096735</v>
       </c>
-      <c r="C17" s="97" t="str">
+      <c r="C17" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(4,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pablo Steven Ochoa Rodriguez</v>
       </c>
-      <c r="D17" s="97" t="str">
+      <c r="D17" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(4,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E17" s="99">
+      <c r="E17" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(4,Registro!$T$2:$T$100,0)),"")</f>
         <v>81</v>
       </c>
@@ -14780,93 +14814,93 @@
       </c>
       <c r="G17" s="72"/>
       <c r="H17" s="73"/>
-      <c r="I17" s="91"/>
+      <c r="I17" s="90"/>
       <c r="J17" s="73"/>
-      <c r="K17" s="84"/>
+      <c r="K17" s="102"/>
       <c r="L17" s="71"/>
     </row>
     <row r="18" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A18" s="96"/>
-      <c r="B18" s="98"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="99"/>
+      <c r="A18" s="95"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="98"/>
       <c r="F18" s="70">
         <v>2</v>
       </c>
       <c r="G18" s="72"/>
       <c r="H18" s="73"/>
-      <c r="I18" s="91"/>
+      <c r="I18" s="90"/>
       <c r="J18" s="73"/>
-      <c r="K18" s="84"/>
+      <c r="K18" s="103"/>
       <c r="L18" s="71"/>
     </row>
     <row r="19" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A19" s="96"/>
-      <c r="B19" s="98"/>
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="99"/>
+      <c r="A19" s="95"/>
+      <c r="B19" s="97"/>
+      <c r="C19" s="96"/>
+      <c r="D19" s="96"/>
+      <c r="E19" s="98"/>
       <c r="F19" s="70">
         <v>3</v>
       </c>
       <c r="G19" s="72"/>
       <c r="H19" s="73"/>
-      <c r="I19" s="91"/>
+      <c r="I19" s="90"/>
       <c r="J19" s="73"/>
-      <c r="K19" s="84"/>
+      <c r="K19" s="103"/>
       <c r="L19" s="71"/>
     </row>
     <row r="20" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A20" s="96"/>
-      <c r="B20" s="98"/>
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="99"/>
+      <c r="A20" s="95"/>
+      <c r="B20" s="97"/>
+      <c r="C20" s="96"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="98"/>
       <c r="F20" s="70">
         <v>4</v>
       </c>
       <c r="G20" s="72"/>
       <c r="H20" s="73"/>
-      <c r="I20" s="91"/>
+      <c r="I20" s="90"/>
       <c r="J20" s="73"/>
-      <c r="K20" s="84"/>
+      <c r="K20" s="103"/>
       <c r="L20" s="71"/>
     </row>
     <row r="21" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A21" s="96"/>
-      <c r="B21" s="98"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="99"/>
+      <c r="A21" s="95"/>
+      <c r="B21" s="97"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="96"/>
+      <c r="E21" s="98"/>
       <c r="F21" s="70">
         <v>5</v>
       </c>
       <c r="G21" s="72"/>
       <c r="H21" s="73"/>
-      <c r="I21" s="91"/>
+      <c r="I21" s="90"/>
       <c r="J21" s="73"/>
-      <c r="K21" s="84"/>
+      <c r="K21" s="104"/>
       <c r="L21" s="71"/>
     </row>
     <row r="22" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A22" s="92">
+      <c r="A22" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(5,Registro!$T$2:$T$100,0))="","", 5),"")</f>
         <v>5</v>
       </c>
-      <c r="B22" s="93">
+      <c r="B22" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(5,Registro!$T$2:$T$100,0)),"")</f>
         <v>1004961429</v>
       </c>
-      <c r="C22" s="93" t="str">
+      <c r="C22" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(5,Registro!$T$2:$T$100,0)),"")</f>
         <v>Jhon Stiven Marin Valencia</v>
       </c>
-      <c r="D22" s="93" t="str">
+      <c r="D22" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(5,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E22" s="95">
+      <c r="E22" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(5,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -14875,93 +14909,93 @@
       </c>
       <c r="G22" s="68"/>
       <c r="H22" s="69"/>
-      <c r="I22" s="90"/>
+      <c r="I22" s="89"/>
       <c r="J22" s="69"/>
-      <c r="K22" s="66"/>
+      <c r="K22" s="99"/>
       <c r="L22" s="67"/>
     </row>
     <row r="23" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A23" s="92"/>
-      <c r="B23" s="94"/>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="95"/>
+      <c r="A23" s="91"/>
+      <c r="B23" s="93"/>
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="94"/>
       <c r="F23" s="66">
         <v>2</v>
       </c>
       <c r="G23" s="68"/>
       <c r="H23" s="69"/>
-      <c r="I23" s="90"/>
+      <c r="I23" s="89"/>
       <c r="J23" s="69"/>
-      <c r="K23" s="66"/>
+      <c r="K23" s="100"/>
       <c r="L23" s="67"/>
     </row>
     <row r="24" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A24" s="92"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="93"/>
-      <c r="D24" s="93"/>
-      <c r="E24" s="95"/>
+      <c r="A24" s="91"/>
+      <c r="B24" s="93"/>
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="94"/>
       <c r="F24" s="66">
         <v>3</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="69"/>
-      <c r="I24" s="90"/>
+      <c r="I24" s="89"/>
       <c r="J24" s="69"/>
-      <c r="K24" s="66"/>
+      <c r="K24" s="100"/>
       <c r="L24" s="67"/>
     </row>
     <row r="25" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A25" s="92"/>
-      <c r="B25" s="94"/>
-      <c r="C25" s="93"/>
-      <c r="D25" s="93"/>
-      <c r="E25" s="95"/>
+      <c r="A25" s="91"/>
+      <c r="B25" s="93"/>
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="94"/>
       <c r="F25" s="66">
         <v>4</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="69"/>
-      <c r="I25" s="90"/>
+      <c r="I25" s="89"/>
       <c r="J25" s="69"/>
-      <c r="K25" s="66"/>
+      <c r="K25" s="100"/>
       <c r="L25" s="67"/>
     </row>
     <row r="26" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A26" s="92"/>
-      <c r="B26" s="94"/>
-      <c r="C26" s="93"/>
-      <c r="D26" s="93"/>
-      <c r="E26" s="95"/>
+      <c r="A26" s="91"/>
+      <c r="B26" s="93"/>
+      <c r="C26" s="92"/>
+      <c r="D26" s="92"/>
+      <c r="E26" s="94"/>
       <c r="F26" s="66">
         <v>5</v>
       </c>
       <c r="G26" s="68"/>
       <c r="H26" s="69"/>
-      <c r="I26" s="90"/>
+      <c r="I26" s="89"/>
       <c r="J26" s="69"/>
-      <c r="K26" s="66"/>
+      <c r="K26" s="101"/>
       <c r="L26" s="67"/>
     </row>
     <row r="27" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A27" s="96">
+      <c r="A27" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(6,Registro!$T$2:$T$100,0))="","", 6),"")</f>
         <v>6</v>
       </c>
-      <c r="B27" s="97">
+      <c r="B27" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(6,Registro!$T$2:$T$100,0)),"")</f>
         <v>53121281</v>
       </c>
-      <c r="C27" s="97" t="str">
+      <c r="C27" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(6,Registro!$T$2:$T$100,0)),"")</f>
         <v>Yulieth Paola Rodriguez Cañon</v>
       </c>
-      <c r="D27" s="97" t="str">
+      <c r="D27" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(6,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E27" s="99">
+      <c r="E27" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(6,Registro!$T$2:$T$100,0)),"")</f>
         <v>78</v>
       </c>
@@ -14970,93 +15004,93 @@
       </c>
       <c r="G27" s="72"/>
       <c r="H27" s="73"/>
-      <c r="I27" s="91"/>
+      <c r="I27" s="90"/>
       <c r="J27" s="73"/>
-      <c r="K27" s="84"/>
+      <c r="K27" s="102"/>
       <c r="L27" s="71"/>
     </row>
     <row r="28" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A28" s="96"/>
-      <c r="B28" s="98"/>
-      <c r="C28" s="97"/>
-      <c r="D28" s="97"/>
-      <c r="E28" s="99"/>
+      <c r="A28" s="95"/>
+      <c r="B28" s="97"/>
+      <c r="C28" s="96"/>
+      <c r="D28" s="96"/>
+      <c r="E28" s="98"/>
       <c r="F28" s="70">
         <v>2</v>
       </c>
       <c r="G28" s="72"/>
       <c r="H28" s="73"/>
-      <c r="I28" s="91"/>
+      <c r="I28" s="90"/>
       <c r="J28" s="73"/>
-      <c r="K28" s="84"/>
+      <c r="K28" s="103"/>
       <c r="L28" s="71"/>
     </row>
     <row r="29" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A29" s="96"/>
-      <c r="B29" s="98"/>
-      <c r="C29" s="97"/>
-      <c r="D29" s="97"/>
-      <c r="E29" s="99"/>
+      <c r="A29" s="95"/>
+      <c r="B29" s="97"/>
+      <c r="C29" s="96"/>
+      <c r="D29" s="96"/>
+      <c r="E29" s="98"/>
       <c r="F29" s="70">
         <v>3</v>
       </c>
       <c r="G29" s="72"/>
       <c r="H29" s="73"/>
-      <c r="I29" s="91"/>
+      <c r="I29" s="90"/>
       <c r="J29" s="73"/>
-      <c r="K29" s="84"/>
+      <c r="K29" s="103"/>
       <c r="L29" s="71"/>
     </row>
     <row r="30" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A30" s="96"/>
-      <c r="B30" s="98"/>
-      <c r="C30" s="97"/>
-      <c r="D30" s="97"/>
-      <c r="E30" s="99"/>
+      <c r="A30" s="95"/>
+      <c r="B30" s="97"/>
+      <c r="C30" s="96"/>
+      <c r="D30" s="96"/>
+      <c r="E30" s="98"/>
       <c r="F30" s="70">
         <v>4</v>
       </c>
       <c r="G30" s="72"/>
       <c r="H30" s="73"/>
-      <c r="I30" s="91"/>
+      <c r="I30" s="90"/>
       <c r="J30" s="73"/>
-      <c r="K30" s="84"/>
+      <c r="K30" s="103"/>
       <c r="L30" s="71"/>
     </row>
     <row r="31" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A31" s="96"/>
-      <c r="B31" s="98"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="99"/>
+      <c r="A31" s="95"/>
+      <c r="B31" s="97"/>
+      <c r="C31" s="96"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="98"/>
       <c r="F31" s="70">
         <v>5</v>
       </c>
       <c r="G31" s="72"/>
       <c r="H31" s="73"/>
-      <c r="I31" s="91"/>
+      <c r="I31" s="90"/>
       <c r="J31" s="73"/>
-      <c r="K31" s="84"/>
+      <c r="K31" s="104"/>
       <c r="L31" s="71"/>
     </row>
     <row r="32" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A32" s="92">
+      <c r="A32" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(7,Registro!$T$2:$T$100,0))="","", 7),"")</f>
         <v>7</v>
       </c>
-      <c r="B32" s="93">
+      <c r="B32" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(7,Registro!$T$2:$T$100,0)),"")</f>
         <v>1024585365</v>
       </c>
-      <c r="C32" s="93" t="str">
+      <c r="C32" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(7,Registro!$T$2:$T$100,0)),"")</f>
         <v>Cristian David Celis Garcia</v>
       </c>
-      <c r="D32" s="93" t="str">
+      <c r="D32" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(7,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E32" s="95">
+      <c r="E32" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(7,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -15065,93 +15099,93 @@
       </c>
       <c r="G32" s="68"/>
       <c r="H32" s="69"/>
-      <c r="I32" s="90"/>
+      <c r="I32" s="89"/>
       <c r="J32" s="69"/>
-      <c r="K32" s="66"/>
+      <c r="K32" s="99"/>
       <c r="L32" s="67"/>
     </row>
     <row r="33" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A33" s="92"/>
-      <c r="B33" s="94"/>
-      <c r="C33" s="93"/>
-      <c r="D33" s="93"/>
-      <c r="E33" s="95"/>
+      <c r="A33" s="91"/>
+      <c r="B33" s="93"/>
+      <c r="C33" s="92"/>
+      <c r="D33" s="92"/>
+      <c r="E33" s="94"/>
       <c r="F33" s="66">
         <v>2</v>
       </c>
       <c r="G33" s="68"/>
       <c r="H33" s="69"/>
-      <c r="I33" s="90"/>
+      <c r="I33" s="89"/>
       <c r="J33" s="69"/>
-      <c r="K33" s="66"/>
+      <c r="K33" s="100"/>
       <c r="L33" s="67"/>
     </row>
     <row r="34" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A34" s="92"/>
-      <c r="B34" s="94"/>
-      <c r="C34" s="93"/>
-      <c r="D34" s="93"/>
-      <c r="E34" s="95"/>
+      <c r="A34" s="91"/>
+      <c r="B34" s="93"/>
+      <c r="C34" s="92"/>
+      <c r="D34" s="92"/>
+      <c r="E34" s="94"/>
       <c r="F34" s="66">
         <v>3</v>
       </c>
       <c r="G34" s="68"/>
       <c r="H34" s="69"/>
-      <c r="I34" s="90"/>
+      <c r="I34" s="89"/>
       <c r="J34" s="69"/>
-      <c r="K34" s="66"/>
+      <c r="K34" s="100"/>
       <c r="L34" s="67"/>
     </row>
     <row r="35" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A35" s="92"/>
-      <c r="B35" s="94"/>
-      <c r="C35" s="93"/>
-      <c r="D35" s="93"/>
-      <c r="E35" s="95"/>
+      <c r="A35" s="91"/>
+      <c r="B35" s="93"/>
+      <c r="C35" s="92"/>
+      <c r="D35" s="92"/>
+      <c r="E35" s="94"/>
       <c r="F35" s="66">
         <v>4</v>
       </c>
       <c r="G35" s="68"/>
       <c r="H35" s="69"/>
-      <c r="I35" s="90"/>
+      <c r="I35" s="89"/>
       <c r="J35" s="69"/>
-      <c r="K35" s="66"/>
+      <c r="K35" s="100"/>
       <c r="L35" s="67"/>
     </row>
     <row r="36" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A36" s="92"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="93"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="95"/>
+      <c r="A36" s="91"/>
+      <c r="B36" s="93"/>
+      <c r="C36" s="92"/>
+      <c r="D36" s="92"/>
+      <c r="E36" s="94"/>
       <c r="F36" s="66">
         <v>5</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="69"/>
-      <c r="I36" s="90"/>
+      <c r="I36" s="89"/>
       <c r="J36" s="69"/>
-      <c r="K36" s="66"/>
+      <c r="K36" s="101"/>
       <c r="L36" s="67"/>
     </row>
     <row r="37" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A37" s="96">
+      <c r="A37" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(8,Registro!$T$2:$T$100,0))="","", 8),"")</f>
         <v>8</v>
       </c>
-      <c r="B37" s="97">
+      <c r="B37" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(8,Registro!$T$2:$T$100,0)),"")</f>
         <v>1000547797</v>
       </c>
-      <c r="C37" s="97" t="str">
+      <c r="C37" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(8,Registro!$T$2:$T$100,0)),"")</f>
         <v>Kamy Lizeth Rios Gomez</v>
       </c>
-      <c r="D37" s="97" t="str">
+      <c r="D37" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(8,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E37" s="99">
+      <c r="E37" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(8,Registro!$T$2:$T$100,0)),"")</f>
         <v>90</v>
       </c>
@@ -15160,93 +15194,93 @@
       </c>
       <c r="G37" s="72"/>
       <c r="H37" s="73"/>
-      <c r="I37" s="91"/>
+      <c r="I37" s="90"/>
       <c r="J37" s="73"/>
-      <c r="K37" s="84"/>
+      <c r="K37" s="102"/>
       <c r="L37" s="71"/>
     </row>
     <row r="38" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A38" s="96"/>
-      <c r="B38" s="98"/>
-      <c r="C38" s="97"/>
-      <c r="D38" s="97"/>
-      <c r="E38" s="99"/>
+      <c r="A38" s="95"/>
+      <c r="B38" s="97"/>
+      <c r="C38" s="96"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="98"/>
       <c r="F38" s="70">
         <v>2</v>
       </c>
       <c r="G38" s="72"/>
       <c r="H38" s="73"/>
-      <c r="I38" s="91"/>
+      <c r="I38" s="90"/>
       <c r="J38" s="73"/>
-      <c r="K38" s="84"/>
+      <c r="K38" s="103"/>
       <c r="L38" s="71"/>
     </row>
     <row r="39" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A39" s="96"/>
-      <c r="B39" s="98"/>
-      <c r="C39" s="97"/>
-      <c r="D39" s="97"/>
-      <c r="E39" s="99"/>
+      <c r="A39" s="95"/>
+      <c r="B39" s="97"/>
+      <c r="C39" s="96"/>
+      <c r="D39" s="96"/>
+      <c r="E39" s="98"/>
       <c r="F39" s="70">
         <v>3</v>
       </c>
       <c r="G39" s="72"/>
       <c r="H39" s="73"/>
-      <c r="I39" s="91"/>
+      <c r="I39" s="90"/>
       <c r="J39" s="73"/>
-      <c r="K39" s="84"/>
+      <c r="K39" s="103"/>
       <c r="L39" s="71"/>
     </row>
     <row r="40" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A40" s="96"/>
-      <c r="B40" s="98"/>
-      <c r="C40" s="97"/>
-      <c r="D40" s="97"/>
-      <c r="E40" s="99"/>
+      <c r="A40" s="95"/>
+      <c r="B40" s="97"/>
+      <c r="C40" s="96"/>
+      <c r="D40" s="96"/>
+      <c r="E40" s="98"/>
       <c r="F40" s="70">
         <v>4</v>
       </c>
       <c r="G40" s="72"/>
       <c r="H40" s="73"/>
-      <c r="I40" s="91"/>
+      <c r="I40" s="90"/>
       <c r="J40" s="73"/>
-      <c r="K40" s="84"/>
+      <c r="K40" s="103"/>
       <c r="L40" s="71"/>
     </row>
     <row r="41" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A41" s="96"/>
-      <c r="B41" s="98"/>
-      <c r="C41" s="97"/>
-      <c r="D41" s="97"/>
-      <c r="E41" s="99"/>
+      <c r="A41" s="95"/>
+      <c r="B41" s="97"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="98"/>
       <c r="F41" s="70">
         <v>5</v>
       </c>
       <c r="G41" s="72"/>
       <c r="H41" s="73"/>
-      <c r="I41" s="91"/>
+      <c r="I41" s="90"/>
       <c r="J41" s="73"/>
-      <c r="K41" s="84"/>
+      <c r="K41" s="104"/>
       <c r="L41" s="71"/>
     </row>
     <row r="42" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A42" s="92">
+      <c r="A42" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(9,Registro!$T$2:$T$100,0))="","", 9),"")</f>
         <v>9</v>
       </c>
-      <c r="B42" s="93">
+      <c r="B42" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(9,Registro!$T$2:$T$100,0)),"")</f>
         <v>1023867138</v>
       </c>
-      <c r="C42" s="93" t="str">
+      <c r="C42" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(9,Registro!$T$2:$T$100,0)),"")</f>
         <v>Yisell Dayana Castro González</v>
       </c>
-      <c r="D42" s="93" t="str">
+      <c r="D42" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(9,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E42" s="95">
+      <c r="E42" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(9,Registro!$T$2:$T$100,0)),"")</f>
         <v>72</v>
       </c>
@@ -15255,93 +15289,93 @@
       </c>
       <c r="G42" s="68"/>
       <c r="H42" s="69"/>
-      <c r="I42" s="90"/>
+      <c r="I42" s="89"/>
       <c r="J42" s="69"/>
-      <c r="K42" s="66"/>
+      <c r="K42" s="99"/>
       <c r="L42" s="67"/>
     </row>
     <row r="43" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A43" s="92"/>
-      <c r="B43" s="94"/>
-      <c r="C43" s="93"/>
-      <c r="D43" s="93"/>
-      <c r="E43" s="95"/>
+      <c r="A43" s="91"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="92"/>
+      <c r="D43" s="92"/>
+      <c r="E43" s="94"/>
       <c r="F43" s="66">
         <v>2</v>
       </c>
       <c r="G43" s="68"/>
       <c r="H43" s="69"/>
-      <c r="I43" s="90"/>
+      <c r="I43" s="89"/>
       <c r="J43" s="69"/>
-      <c r="K43" s="66"/>
+      <c r="K43" s="100"/>
       <c r="L43" s="67"/>
     </row>
     <row r="44" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A44" s="92"/>
-      <c r="B44" s="94"/>
-      <c r="C44" s="93"/>
-      <c r="D44" s="93"/>
-      <c r="E44" s="95"/>
+      <c r="A44" s="91"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="94"/>
       <c r="F44" s="66">
         <v>3</v>
       </c>
       <c r="G44" s="68"/>
       <c r="H44" s="69"/>
-      <c r="I44" s="90"/>
+      <c r="I44" s="89"/>
       <c r="J44" s="69"/>
-      <c r="K44" s="66"/>
+      <c r="K44" s="100"/>
       <c r="L44" s="67"/>
     </row>
     <row r="45" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A45" s="92"/>
-      <c r="B45" s="94"/>
-      <c r="C45" s="93"/>
-      <c r="D45" s="93"/>
-      <c r="E45" s="95"/>
+      <c r="A45" s="91"/>
+      <c r="B45" s="93"/>
+      <c r="C45" s="92"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="94"/>
       <c r="F45" s="66">
         <v>4</v>
       </c>
       <c r="G45" s="68"/>
       <c r="H45" s="69"/>
-      <c r="I45" s="90"/>
+      <c r="I45" s="89"/>
       <c r="J45" s="69"/>
-      <c r="K45" s="66"/>
+      <c r="K45" s="100"/>
       <c r="L45" s="67"/>
     </row>
     <row r="46" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A46" s="92"/>
-      <c r="B46" s="94"/>
-      <c r="C46" s="93"/>
-      <c r="D46" s="93"/>
-      <c r="E46" s="95"/>
+      <c r="A46" s="91"/>
+      <c r="B46" s="93"/>
+      <c r="C46" s="92"/>
+      <c r="D46" s="92"/>
+      <c r="E46" s="94"/>
       <c r="F46" s="66">
         <v>5</v>
       </c>
       <c r="G46" s="68"/>
       <c r="H46" s="69"/>
-      <c r="I46" s="90"/>
+      <c r="I46" s="89"/>
       <c r="J46" s="69"/>
-      <c r="K46" s="66"/>
+      <c r="K46" s="101"/>
       <c r="L46" s="67"/>
     </row>
     <row r="47" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A47" s="96">
+      <c r="A47" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(10,Registro!$T$2:$T$100,0))="","", 10),"")</f>
         <v>10</v>
       </c>
-      <c r="B47" s="97">
+      <c r="B47" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(10,Registro!$T$2:$T$100,0)),"")</f>
         <v>1000810776</v>
       </c>
-      <c r="C47" s="97" t="str">
+      <c r="C47" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(10,Registro!$T$2:$T$100,0)),"")</f>
         <v>Nataly Andrea Maecha Lizarazo</v>
       </c>
-      <c r="D47" s="97" t="str">
+      <c r="D47" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(10,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E47" s="99">
+      <c r="E47" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(10,Registro!$T$2:$T$100,0)),"")</f>
         <v>74</v>
       </c>
@@ -15350,93 +15384,93 @@
       </c>
       <c r="G47" s="72"/>
       <c r="H47" s="73"/>
-      <c r="I47" s="91"/>
+      <c r="I47" s="90"/>
       <c r="J47" s="73"/>
-      <c r="K47" s="84"/>
+      <c r="K47" s="102"/>
       <c r="L47" s="71"/>
     </row>
     <row r="48" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A48" s="96"/>
-      <c r="B48" s="98"/>
-      <c r="C48" s="97"/>
-      <c r="D48" s="97"/>
-      <c r="E48" s="99"/>
+      <c r="A48" s="95"/>
+      <c r="B48" s="97"/>
+      <c r="C48" s="96"/>
+      <c r="D48" s="96"/>
+      <c r="E48" s="98"/>
       <c r="F48" s="70">
         <v>2</v>
       </c>
       <c r="G48" s="72"/>
       <c r="H48" s="73"/>
-      <c r="I48" s="91"/>
+      <c r="I48" s="90"/>
       <c r="J48" s="73"/>
-      <c r="K48" s="84"/>
+      <c r="K48" s="103"/>
       <c r="L48" s="71"/>
     </row>
     <row r="49" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A49" s="96"/>
-      <c r="B49" s="98"/>
-      <c r="C49" s="97"/>
-      <c r="D49" s="97"/>
-      <c r="E49" s="99"/>
+      <c r="A49" s="95"/>
+      <c r="B49" s="97"/>
+      <c r="C49" s="96"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="98"/>
       <c r="F49" s="70">
         <v>3</v>
       </c>
       <c r="G49" s="72"/>
       <c r="H49" s="73"/>
-      <c r="I49" s="91"/>
+      <c r="I49" s="90"/>
       <c r="J49" s="73"/>
-      <c r="K49" s="84"/>
+      <c r="K49" s="103"/>
       <c r="L49" s="71"/>
     </row>
     <row r="50" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A50" s="96"/>
-      <c r="B50" s="98"/>
-      <c r="C50" s="97"/>
-      <c r="D50" s="97"/>
-      <c r="E50" s="99"/>
+      <c r="A50" s="95"/>
+      <c r="B50" s="97"/>
+      <c r="C50" s="96"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="98"/>
       <c r="F50" s="70">
         <v>4</v>
       </c>
       <c r="G50" s="72"/>
       <c r="H50" s="73"/>
-      <c r="I50" s="91"/>
+      <c r="I50" s="90"/>
       <c r="J50" s="73"/>
-      <c r="K50" s="84"/>
+      <c r="K50" s="103"/>
       <c r="L50" s="71"/>
     </row>
     <row r="51" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A51" s="96"/>
-      <c r="B51" s="98"/>
-      <c r="C51" s="97"/>
-      <c r="D51" s="97"/>
-      <c r="E51" s="99"/>
+      <c r="A51" s="95"/>
+      <c r="B51" s="97"/>
+      <c r="C51" s="96"/>
+      <c r="D51" s="96"/>
+      <c r="E51" s="98"/>
       <c r="F51" s="70">
         <v>5</v>
       </c>
       <c r="G51" s="72"/>
       <c r="H51" s="73"/>
-      <c r="I51" s="91"/>
+      <c r="I51" s="90"/>
       <c r="J51" s="73"/>
-      <c r="K51" s="84"/>
+      <c r="K51" s="104"/>
       <c r="L51" s="71"/>
     </row>
     <row r="52" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A52" s="92">
+      <c r="A52" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(11,Registro!$T$2:$T$100,0))="","", 11),"")</f>
         <v>11</v>
       </c>
-      <c r="B52" s="93">
+      <c r="B52" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(11,Registro!$T$2:$T$100,0)),"")</f>
         <v>1001271946</v>
       </c>
-      <c r="C52" s="93" t="str">
+      <c r="C52" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(11,Registro!$T$2:$T$100,0)),"")</f>
         <v>Luisa Fernanda Rodríguez Sarmiento</v>
       </c>
-      <c r="D52" s="93" t="str">
+      <c r="D52" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(11,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E52" s="95">
+      <c r="E52" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(11,Registro!$T$2:$T$100,0)),"")</f>
         <v>74</v>
       </c>
@@ -15445,93 +15479,93 @@
       </c>
       <c r="G52" s="68"/>
       <c r="H52" s="69"/>
-      <c r="I52" s="90"/>
+      <c r="I52" s="89"/>
       <c r="J52" s="69"/>
-      <c r="K52" s="66"/>
+      <c r="K52" s="99"/>
       <c r="L52" s="67"/>
     </row>
     <row r="53" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A53" s="92"/>
-      <c r="B53" s="94"/>
-      <c r="C53" s="93"/>
-      <c r="D53" s="93"/>
-      <c r="E53" s="95"/>
+      <c r="A53" s="91"/>
+      <c r="B53" s="93"/>
+      <c r="C53" s="92"/>
+      <c r="D53" s="92"/>
+      <c r="E53" s="94"/>
       <c r="F53" s="66">
         <v>2</v>
       </c>
       <c r="G53" s="68"/>
       <c r="H53" s="69"/>
-      <c r="I53" s="90"/>
+      <c r="I53" s="89"/>
       <c r="J53" s="69"/>
-      <c r="K53" s="66"/>
+      <c r="K53" s="100"/>
       <c r="L53" s="67"/>
     </row>
     <row r="54" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A54" s="92"/>
-      <c r="B54" s="94"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="95"/>
+      <c r="A54" s="91"/>
+      <c r="B54" s="93"/>
+      <c r="C54" s="92"/>
+      <c r="D54" s="92"/>
+      <c r="E54" s="94"/>
       <c r="F54" s="66">
         <v>3</v>
       </c>
       <c r="G54" s="68"/>
       <c r="H54" s="69"/>
-      <c r="I54" s="90"/>
+      <c r="I54" s="89"/>
       <c r="J54" s="69"/>
-      <c r="K54" s="66"/>
+      <c r="K54" s="100"/>
       <c r="L54" s="67"/>
     </row>
     <row r="55" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A55" s="92"/>
-      <c r="B55" s="94"/>
-      <c r="C55" s="93"/>
-      <c r="D55" s="93"/>
-      <c r="E55" s="95"/>
+      <c r="A55" s="91"/>
+      <c r="B55" s="93"/>
+      <c r="C55" s="92"/>
+      <c r="D55" s="92"/>
+      <c r="E55" s="94"/>
       <c r="F55" s="66">
         <v>4</v>
       </c>
       <c r="G55" s="68"/>
       <c r="H55" s="69"/>
-      <c r="I55" s="90"/>
+      <c r="I55" s="89"/>
       <c r="J55" s="69"/>
-      <c r="K55" s="66"/>
+      <c r="K55" s="100"/>
       <c r="L55" s="67"/>
     </row>
     <row r="56" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A56" s="92"/>
-      <c r="B56" s="94"/>
-      <c r="C56" s="93"/>
-      <c r="D56" s="93"/>
-      <c r="E56" s="95"/>
+      <c r="A56" s="91"/>
+      <c r="B56" s="93"/>
+      <c r="C56" s="92"/>
+      <c r="D56" s="92"/>
+      <c r="E56" s="94"/>
       <c r="F56" s="66">
         <v>5</v>
       </c>
       <c r="G56" s="68"/>
       <c r="H56" s="69"/>
-      <c r="I56" s="90"/>
+      <c r="I56" s="89"/>
       <c r="J56" s="69"/>
-      <c r="K56" s="66"/>
+      <c r="K56" s="101"/>
       <c r="L56" s="67"/>
     </row>
     <row r="57" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A57" s="96">
+      <c r="A57" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(12,Registro!$T$2:$T$100,0))="","", 12),"")</f>
         <v>12</v>
       </c>
-      <c r="B57" s="97">
+      <c r="B57" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(12,Registro!$T$2:$T$100,0)),"")</f>
         <v>1117813165</v>
       </c>
-      <c r="C57" s="97" t="str">
+      <c r="C57" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(12,Registro!$T$2:$T$100,0)),"")</f>
         <v>Yedinson Stiven Ramirez Perdómo</v>
       </c>
-      <c r="D57" s="97" t="str">
+      <c r="D57" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(12,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E57" s="99">
+      <c r="E57" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(12,Registro!$T$2:$T$100,0)),"")</f>
         <v>94</v>
       </c>
@@ -15540,93 +15574,93 @@
       </c>
       <c r="G57" s="72"/>
       <c r="H57" s="73"/>
-      <c r="I57" s="91"/>
+      <c r="I57" s="90"/>
       <c r="J57" s="73"/>
-      <c r="K57" s="84"/>
+      <c r="K57" s="102"/>
       <c r="L57" s="71"/>
     </row>
     <row r="58" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A58" s="96"/>
-      <c r="B58" s="98"/>
-      <c r="C58" s="97"/>
-      <c r="D58" s="97"/>
-      <c r="E58" s="99"/>
+      <c r="A58" s="95"/>
+      <c r="B58" s="97"/>
+      <c r="C58" s="96"/>
+      <c r="D58" s="96"/>
+      <c r="E58" s="98"/>
       <c r="F58" s="70">
         <v>2</v>
       </c>
       <c r="G58" s="72"/>
       <c r="H58" s="73"/>
-      <c r="I58" s="91"/>
+      <c r="I58" s="90"/>
       <c r="J58" s="73"/>
-      <c r="K58" s="84"/>
+      <c r="K58" s="103"/>
       <c r="L58" s="71"/>
     </row>
     <row r="59" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A59" s="96"/>
-      <c r="B59" s="98"/>
-      <c r="C59" s="97"/>
-      <c r="D59" s="97"/>
-      <c r="E59" s="99"/>
+      <c r="A59" s="95"/>
+      <c r="B59" s="97"/>
+      <c r="C59" s="96"/>
+      <c r="D59" s="96"/>
+      <c r="E59" s="98"/>
       <c r="F59" s="70">
         <v>3</v>
       </c>
       <c r="G59" s="72"/>
       <c r="H59" s="73"/>
-      <c r="I59" s="91"/>
+      <c r="I59" s="90"/>
       <c r="J59" s="73"/>
-      <c r="K59" s="84"/>
+      <c r="K59" s="103"/>
       <c r="L59" s="71"/>
     </row>
     <row r="60" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A60" s="96"/>
-      <c r="B60" s="98"/>
-      <c r="C60" s="97"/>
-      <c r="D60" s="97"/>
-      <c r="E60" s="99"/>
+      <c r="A60" s="95"/>
+      <c r="B60" s="97"/>
+      <c r="C60" s="96"/>
+      <c r="D60" s="96"/>
+      <c r="E60" s="98"/>
       <c r="F60" s="70">
         <v>4</v>
       </c>
       <c r="G60" s="72"/>
       <c r="H60" s="73"/>
-      <c r="I60" s="91"/>
+      <c r="I60" s="90"/>
       <c r="J60" s="73"/>
-      <c r="K60" s="84"/>
+      <c r="K60" s="103"/>
       <c r="L60" s="71"/>
     </row>
     <row r="61" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A61" s="96"/>
-      <c r="B61" s="98"/>
-      <c r="C61" s="97"/>
-      <c r="D61" s="97"/>
-      <c r="E61" s="99"/>
+      <c r="A61" s="95"/>
+      <c r="B61" s="97"/>
+      <c r="C61" s="96"/>
+      <c r="D61" s="96"/>
+      <c r="E61" s="98"/>
       <c r="F61" s="70">
         <v>5</v>
       </c>
       <c r="G61" s="72"/>
       <c r="H61" s="73"/>
-      <c r="I61" s="91"/>
+      <c r="I61" s="90"/>
       <c r="J61" s="73"/>
-      <c r="K61" s="84"/>
+      <c r="K61" s="104"/>
       <c r="L61" s="71"/>
     </row>
     <row r="62" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A62" s="92">
+      <c r="A62" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(13,Registro!$T$2:$T$100,0))="","", 13),"")</f>
         <v>13</v>
       </c>
-      <c r="B62" s="93">
+      <c r="B62" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(13,Registro!$T$2:$T$100,0)),"")</f>
         <v>1070595836</v>
       </c>
-      <c r="C62" s="93" t="str">
+      <c r="C62" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(13,Registro!$T$2:$T$100,0)),"")</f>
         <v>Hebert Julián Casilimas Ricardo</v>
       </c>
-      <c r="D62" s="93" t="str">
+      <c r="D62" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(13,Registro!$T$2:$T$100,0)),"")</f>
         <v>Posgrados</v>
       </c>
-      <c r="E62" s="95">
+      <c r="E62" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(13,Registro!$T$2:$T$100,0)),"")</f>
         <v>91</v>
       </c>
@@ -15635,93 +15669,93 @@
       </c>
       <c r="G62" s="68"/>
       <c r="H62" s="69"/>
-      <c r="I62" s="90"/>
+      <c r="I62" s="89"/>
       <c r="J62" s="69"/>
-      <c r="K62" s="66"/>
+      <c r="K62" s="99"/>
       <c r="L62" s="67"/>
     </row>
     <row r="63" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A63" s="92"/>
-      <c r="B63" s="94"/>
-      <c r="C63" s="93"/>
-      <c r="D63" s="93"/>
-      <c r="E63" s="95"/>
+      <c r="A63" s="91"/>
+      <c r="B63" s="93"/>
+      <c r="C63" s="92"/>
+      <c r="D63" s="92"/>
+      <c r="E63" s="94"/>
       <c r="F63" s="66">
         <v>2</v>
       </c>
       <c r="G63" s="68"/>
       <c r="H63" s="69"/>
-      <c r="I63" s="90"/>
+      <c r="I63" s="89"/>
       <c r="J63" s="69"/>
-      <c r="K63" s="66"/>
+      <c r="K63" s="100"/>
       <c r="L63" s="67"/>
     </row>
     <row r="64" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A64" s="92"/>
-      <c r="B64" s="94"/>
-      <c r="C64" s="93"/>
-      <c r="D64" s="93"/>
-      <c r="E64" s="95"/>
+      <c r="A64" s="91"/>
+      <c r="B64" s="93"/>
+      <c r="C64" s="92"/>
+      <c r="D64" s="92"/>
+      <c r="E64" s="94"/>
       <c r="F64" s="66">
         <v>3</v>
       </c>
       <c r="G64" s="68"/>
       <c r="H64" s="69"/>
-      <c r="I64" s="90"/>
+      <c r="I64" s="89"/>
       <c r="J64" s="69"/>
-      <c r="K64" s="66"/>
+      <c r="K64" s="100"/>
       <c r="L64" s="67"/>
     </row>
     <row r="65" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A65" s="92"/>
-      <c r="B65" s="94"/>
-      <c r="C65" s="93"/>
-      <c r="D65" s="93"/>
-      <c r="E65" s="95"/>
+      <c r="A65" s="91"/>
+      <c r="B65" s="93"/>
+      <c r="C65" s="92"/>
+      <c r="D65" s="92"/>
+      <c r="E65" s="94"/>
       <c r="F65" s="66">
         <v>4</v>
       </c>
       <c r="G65" s="68"/>
       <c r="H65" s="69"/>
-      <c r="I65" s="90"/>
+      <c r="I65" s="89"/>
       <c r="J65" s="69"/>
-      <c r="K65" s="66"/>
+      <c r="K65" s="100"/>
       <c r="L65" s="67"/>
     </row>
     <row r="66" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A66" s="92"/>
-      <c r="B66" s="94"/>
-      <c r="C66" s="93"/>
-      <c r="D66" s="93"/>
-      <c r="E66" s="95"/>
+      <c r="A66" s="91"/>
+      <c r="B66" s="93"/>
+      <c r="C66" s="92"/>
+      <c r="D66" s="92"/>
+      <c r="E66" s="94"/>
       <c r="F66" s="66">
         <v>5</v>
       </c>
       <c r="G66" s="68"/>
       <c r="H66" s="69"/>
-      <c r="I66" s="90"/>
+      <c r="I66" s="89"/>
       <c r="J66" s="69"/>
-      <c r="K66" s="66"/>
+      <c r="K66" s="101"/>
       <c r="L66" s="67"/>
     </row>
     <row r="67" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A67" s="96">
+      <c r="A67" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(14,Registro!$T$2:$T$100,0))="","", 14),"")</f>
         <v>14</v>
       </c>
-      <c r="B67" s="97">
+      <c r="B67" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(14,Registro!$T$2:$T$100,0)),"")</f>
         <v>1012455544</v>
       </c>
-      <c r="C67" s="97" t="str">
+      <c r="C67" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(14,Registro!$T$2:$T$100,0)),"")</f>
         <v xml:space="preserve">Claudia Yadira Suta Torres </v>
       </c>
-      <c r="D67" s="97" t="str">
+      <c r="D67" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(14,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E67" s="99">
+      <c r="E67" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(14,Registro!$T$2:$T$100,0)),"")</f>
         <v>74</v>
       </c>
@@ -15730,93 +15764,93 @@
       </c>
       <c r="G67" s="72"/>
       <c r="H67" s="73"/>
-      <c r="I67" s="91"/>
+      <c r="I67" s="90"/>
       <c r="J67" s="73"/>
-      <c r="K67" s="84"/>
+      <c r="K67" s="105"/>
       <c r="L67" s="71"/>
     </row>
     <row r="68" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A68" s="96"/>
-      <c r="B68" s="98"/>
-      <c r="C68" s="97"/>
-      <c r="D68" s="97"/>
-      <c r="E68" s="99"/>
+      <c r="A68" s="95"/>
+      <c r="B68" s="97"/>
+      <c r="C68" s="96"/>
+      <c r="D68" s="96"/>
+      <c r="E68" s="98"/>
       <c r="F68" s="70">
         <v>2</v>
       </c>
       <c r="G68" s="72"/>
       <c r="H68" s="73"/>
-      <c r="I68" s="91"/>
+      <c r="I68" s="90"/>
       <c r="J68" s="73"/>
-      <c r="K68" s="84"/>
+      <c r="K68" s="106"/>
       <c r="L68" s="71"/>
     </row>
     <row r="69" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A69" s="96"/>
-      <c r="B69" s="98"/>
-      <c r="C69" s="97"/>
-      <c r="D69" s="97"/>
-      <c r="E69" s="99"/>
+      <c r="A69" s="95"/>
+      <c r="B69" s="97"/>
+      <c r="C69" s="96"/>
+      <c r="D69" s="96"/>
+      <c r="E69" s="98"/>
       <c r="F69" s="70">
         <v>3</v>
       </c>
       <c r="G69" s="72"/>
       <c r="H69" s="73"/>
-      <c r="I69" s="91"/>
+      <c r="I69" s="90"/>
       <c r="J69" s="73"/>
-      <c r="K69" s="84"/>
+      <c r="K69" s="106"/>
       <c r="L69" s="71"/>
     </row>
     <row r="70" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A70" s="96"/>
-      <c r="B70" s="98"/>
-      <c r="C70" s="97"/>
-      <c r="D70" s="97"/>
-      <c r="E70" s="99"/>
+      <c r="A70" s="95"/>
+      <c r="B70" s="97"/>
+      <c r="C70" s="96"/>
+      <c r="D70" s="96"/>
+      <c r="E70" s="98"/>
       <c r="F70" s="70">
         <v>4</v>
       </c>
       <c r="G70" s="72"/>
       <c r="H70" s="73"/>
-      <c r="I70" s="91"/>
+      <c r="I70" s="90"/>
       <c r="J70" s="73"/>
-      <c r="K70" s="84"/>
+      <c r="K70" s="106"/>
       <c r="L70" s="71"/>
     </row>
     <row r="71" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A71" s="96"/>
-      <c r="B71" s="98"/>
-      <c r="C71" s="97"/>
-      <c r="D71" s="97"/>
-      <c r="E71" s="99"/>
+      <c r="A71" s="95"/>
+      <c r="B71" s="97"/>
+      <c r="C71" s="96"/>
+      <c r="D71" s="96"/>
+      <c r="E71" s="98"/>
       <c r="F71" s="70">
         <v>5</v>
       </c>
       <c r="G71" s="72"/>
       <c r="H71" s="73"/>
-      <c r="I71" s="91"/>
+      <c r="I71" s="90"/>
       <c r="J71" s="73"/>
-      <c r="K71" s="84"/>
+      <c r="K71" s="107"/>
       <c r="L71" s="71"/>
     </row>
     <row r="72" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A72" s="92">
+      <c r="A72" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(15,Registro!$T$2:$T$100,0))="","", 15),"")</f>
         <v>15</v>
       </c>
-      <c r="B72" s="93">
+      <c r="B72" s="92">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(15,Registro!$T$2:$T$100,0)),"")</f>
         <v>1006118253</v>
       </c>
-      <c r="C72" s="93" t="str">
+      <c r="C72" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(15,Registro!$T$2:$T$100,0)),"")</f>
         <v>Alex Esteban Angarita Lozano</v>
       </c>
-      <c r="D72" s="93" t="str">
+      <c r="D72" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(15,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E72" s="95">
+      <c r="E72" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(15,Registro!$T$2:$T$100,0)),"")</f>
         <v>70</v>
       </c>
@@ -15825,93 +15859,93 @@
       </c>
       <c r="G72" s="68"/>
       <c r="H72" s="69"/>
-      <c r="I72" s="90"/>
+      <c r="I72" s="89"/>
       <c r="J72" s="69"/>
-      <c r="K72" s="66"/>
+      <c r="K72" s="99"/>
       <c r="L72" s="67"/>
     </row>
     <row r="73" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A73" s="92"/>
-      <c r="B73" s="94"/>
-      <c r="C73" s="93"/>
-      <c r="D73" s="93"/>
-      <c r="E73" s="95"/>
+      <c r="A73" s="91"/>
+      <c r="B73" s="93"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="92"/>
+      <c r="E73" s="94"/>
       <c r="F73" s="66">
         <v>2</v>
       </c>
       <c r="G73" s="68"/>
       <c r="H73" s="69"/>
-      <c r="I73" s="90"/>
+      <c r="I73" s="89"/>
       <c r="J73" s="69"/>
-      <c r="K73" s="66"/>
+      <c r="K73" s="100"/>
       <c r="L73" s="67"/>
     </row>
     <row r="74" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A74" s="92"/>
-      <c r="B74" s="94"/>
-      <c r="C74" s="93"/>
-      <c r="D74" s="93"/>
-      <c r="E74" s="95"/>
+      <c r="A74" s="91"/>
+      <c r="B74" s="93"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="92"/>
+      <c r="E74" s="94"/>
       <c r="F74" s="66">
         <v>3</v>
       </c>
       <c r="G74" s="68"/>
       <c r="H74" s="69"/>
-      <c r="I74" s="90"/>
+      <c r="I74" s="89"/>
       <c r="J74" s="69"/>
-      <c r="K74" s="66"/>
+      <c r="K74" s="100"/>
       <c r="L74" s="67"/>
     </row>
     <row r="75" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A75" s="92"/>
-      <c r="B75" s="94"/>
-      <c r="C75" s="93"/>
-      <c r="D75" s="93"/>
-      <c r="E75" s="95"/>
+      <c r="A75" s="91"/>
+      <c r="B75" s="93"/>
+      <c r="C75" s="92"/>
+      <c r="D75" s="92"/>
+      <c r="E75" s="94"/>
       <c r="F75" s="66">
         <v>4</v>
       </c>
       <c r="G75" s="68"/>
       <c r="H75" s="69"/>
-      <c r="I75" s="90"/>
+      <c r="I75" s="89"/>
       <c r="J75" s="69"/>
-      <c r="K75" s="66"/>
+      <c r="K75" s="100"/>
       <c r="L75" s="67"/>
     </row>
     <row r="76" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A76" s="92"/>
-      <c r="B76" s="94"/>
-      <c r="C76" s="93"/>
-      <c r="D76" s="93"/>
-      <c r="E76" s="95"/>
+      <c r="A76" s="91"/>
+      <c r="B76" s="93"/>
+      <c r="C76" s="92"/>
+      <c r="D76" s="92"/>
+      <c r="E76" s="94"/>
       <c r="F76" s="66">
         <v>5</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="69"/>
-      <c r="I76" s="90"/>
+      <c r="I76" s="89"/>
       <c r="J76" s="69"/>
-      <c r="K76" s="66"/>
+      <c r="K76" s="101"/>
       <c r="L76" s="67"/>
     </row>
     <row r="77" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A77" s="96">
+      <c r="A77" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(16,Registro!$T$2:$T$100,0))="","", 16),"")</f>
         <v>16</v>
       </c>
-      <c r="B77" s="97">
+      <c r="B77" s="96">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(16,Registro!$T$2:$T$100,0)),"")</f>
         <v>1007343398</v>
       </c>
-      <c r="C77" s="97" t="str">
+      <c r="C77" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(16,Registro!$T$2:$T$100,0)),"")</f>
         <v>Duvan Alejandro Díaz Landinez</v>
       </c>
-      <c r="D77" s="97" t="str">
+      <c r="D77" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(16,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E77" s="99">
+      <c r="E77" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(16,Registro!$T$2:$T$100,0)),"")</f>
         <v>74</v>
       </c>
@@ -15920,93 +15954,93 @@
       </c>
       <c r="G77" s="72"/>
       <c r="H77" s="73"/>
-      <c r="I77" s="91"/>
+      <c r="I77" s="90"/>
       <c r="J77" s="73"/>
-      <c r="K77" s="84"/>
+      <c r="K77" s="102"/>
       <c r="L77" s="71"/>
     </row>
     <row r="78" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A78" s="96"/>
-      <c r="B78" s="98"/>
-      <c r="C78" s="97"/>
-      <c r="D78" s="97"/>
-      <c r="E78" s="99"/>
+      <c r="A78" s="95"/>
+      <c r="B78" s="97"/>
+      <c r="C78" s="96"/>
+      <c r="D78" s="96"/>
+      <c r="E78" s="98"/>
       <c r="F78" s="70">
         <v>2</v>
       </c>
       <c r="G78" s="72"/>
       <c r="H78" s="73"/>
-      <c r="I78" s="91"/>
+      <c r="I78" s="90"/>
       <c r="J78" s="73"/>
-      <c r="K78" s="84"/>
+      <c r="K78" s="103"/>
       <c r="L78" s="71"/>
     </row>
     <row r="79" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A79" s="96"/>
-      <c r="B79" s="98"/>
-      <c r="C79" s="97"/>
-      <c r="D79" s="97"/>
-      <c r="E79" s="99"/>
+      <c r="A79" s="95"/>
+      <c r="B79" s="97"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="96"/>
+      <c r="E79" s="98"/>
       <c r="F79" s="70">
         <v>3</v>
       </c>
       <c r="G79" s="72"/>
       <c r="H79" s="73"/>
-      <c r="I79" s="91"/>
+      <c r="I79" s="90"/>
       <c r="J79" s="73"/>
-      <c r="K79" s="84"/>
+      <c r="K79" s="103"/>
       <c r="L79" s="71"/>
     </row>
     <row r="80" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A80" s="96"/>
-      <c r="B80" s="98"/>
-      <c r="C80" s="97"/>
-      <c r="D80" s="97"/>
-      <c r="E80" s="99"/>
+      <c r="A80" s="95"/>
+      <c r="B80" s="97"/>
+      <c r="C80" s="96"/>
+      <c r="D80" s="96"/>
+      <c r="E80" s="98"/>
       <c r="F80" s="70">
         <v>4</v>
       </c>
       <c r="G80" s="72"/>
       <c r="H80" s="73"/>
-      <c r="I80" s="91"/>
+      <c r="I80" s="90"/>
       <c r="J80" s="73"/>
-      <c r="K80" s="84"/>
+      <c r="K80" s="103"/>
       <c r="L80" s="71"/>
     </row>
     <row r="81" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A81" s="96"/>
-      <c r="B81" s="98"/>
-      <c r="C81" s="97"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="99"/>
+      <c r="A81" s="95"/>
+      <c r="B81" s="97"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="96"/>
+      <c r="E81" s="98"/>
       <c r="F81" s="70">
         <v>5</v>
       </c>
       <c r="G81" s="72"/>
       <c r="H81" s="73"/>
-      <c r="I81" s="91"/>
+      <c r="I81" s="90"/>
       <c r="J81" s="73"/>
-      <c r="K81" s="84"/>
+      <c r="K81" s="104"/>
       <c r="L81" s="71"/>
     </row>
     <row r="82" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A82" s="92">
+      <c r="A82" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(17,Registro!$T$2:$T$100,0))="","", 17),"")</f>
         <v>17</v>
       </c>
-      <c r="B82" s="93" t="str">
+      <c r="B82" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(17,Registro!$T$2:$T$100,0)),"")</f>
         <v>1016001445</v>
       </c>
-      <c r="C82" s="93" t="str">
+      <c r="C82" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(17,Registro!$T$2:$T$100,0)),"")</f>
         <v>Norvey Ibarra Marquez</v>
       </c>
-      <c r="D82" s="93" t="str">
+      <c r="D82" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(17,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E82" s="95">
+      <c r="E82" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(17,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -16015,93 +16049,93 @@
       </c>
       <c r="G82" s="68"/>
       <c r="H82" s="69"/>
-      <c r="I82" s="90"/>
+      <c r="I82" s="89"/>
       <c r="J82" s="69"/>
-      <c r="K82" s="66"/>
+      <c r="K82" s="99"/>
       <c r="L82" s="67"/>
     </row>
     <row r="83" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A83" s="92"/>
-      <c r="B83" s="94"/>
-      <c r="C83" s="93"/>
-      <c r="D83" s="93"/>
-      <c r="E83" s="95"/>
+      <c r="A83" s="91"/>
+      <c r="B83" s="93"/>
+      <c r="C83" s="92"/>
+      <c r="D83" s="92"/>
+      <c r="E83" s="94"/>
       <c r="F83" s="66">
         <v>2</v>
       </c>
       <c r="G83" s="68"/>
       <c r="H83" s="69"/>
-      <c r="I83" s="90"/>
+      <c r="I83" s="89"/>
       <c r="J83" s="69"/>
-      <c r="K83" s="66"/>
+      <c r="K83" s="100"/>
       <c r="L83" s="67"/>
     </row>
     <row r="84" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A84" s="92"/>
-      <c r="B84" s="94"/>
-      <c r="C84" s="93"/>
-      <c r="D84" s="93"/>
-      <c r="E84" s="95"/>
+      <c r="A84" s="91"/>
+      <c r="B84" s="93"/>
+      <c r="C84" s="92"/>
+      <c r="D84" s="92"/>
+      <c r="E84" s="94"/>
       <c r="F84" s="66">
         <v>3</v>
       </c>
       <c r="G84" s="68"/>
       <c r="H84" s="69"/>
-      <c r="I84" s="90"/>
+      <c r="I84" s="89"/>
       <c r="J84" s="69"/>
-      <c r="K84" s="66"/>
+      <c r="K84" s="100"/>
       <c r="L84" s="67"/>
     </row>
     <row r="85" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A85" s="92"/>
-      <c r="B85" s="94"/>
-      <c r="C85" s="93"/>
-      <c r="D85" s="93"/>
-      <c r="E85" s="95"/>
+      <c r="A85" s="91"/>
+      <c r="B85" s="93"/>
+      <c r="C85" s="92"/>
+      <c r="D85" s="92"/>
+      <c r="E85" s="94"/>
       <c r="F85" s="66">
         <v>4</v>
       </c>
       <c r="G85" s="68"/>
       <c r="H85" s="69"/>
-      <c r="I85" s="90"/>
+      <c r="I85" s="89"/>
       <c r="J85" s="69"/>
-      <c r="K85" s="66"/>
+      <c r="K85" s="100"/>
       <c r="L85" s="67"/>
     </row>
     <row r="86" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A86" s="92"/>
-      <c r="B86" s="94"/>
-      <c r="C86" s="93"/>
-      <c r="D86" s="93"/>
-      <c r="E86" s="95"/>
+      <c r="A86" s="91"/>
+      <c r="B86" s="93"/>
+      <c r="C86" s="92"/>
+      <c r="D86" s="92"/>
+      <c r="E86" s="94"/>
       <c r="F86" s="66">
         <v>5</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="69"/>
-      <c r="I86" s="90"/>
+      <c r="I86" s="89"/>
       <c r="J86" s="69"/>
-      <c r="K86" s="66"/>
+      <c r="K86" s="101"/>
       <c r="L86" s="67"/>
     </row>
     <row r="87" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A87" s="96">
+      <c r="A87" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(18,Registro!$T$2:$T$100,0))="","", 18),"")</f>
         <v>18</v>
       </c>
-      <c r="B87" s="97" t="str">
+      <c r="B87" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(18,Registro!$T$2:$T$100,0)),"")</f>
         <v>1111332054</v>
       </c>
-      <c r="C87" s="97" t="str">
+      <c r="C87" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(18,Registro!$T$2:$T$100,0)),"")</f>
         <v>Eimi Lisettc Páez Olaya</v>
       </c>
-      <c r="D87" s="97" t="str">
+      <c r="D87" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(18,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E87" s="99">
+      <c r="E87" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(18,Registro!$T$2:$T$100,0)),"")</f>
         <v>75</v>
       </c>
@@ -16110,93 +16144,93 @@
       </c>
       <c r="G87" s="72"/>
       <c r="H87" s="73"/>
-      <c r="I87" s="91"/>
+      <c r="I87" s="90"/>
       <c r="J87" s="73"/>
-      <c r="K87" s="84"/>
+      <c r="K87" s="102"/>
       <c r="L87" s="71"/>
     </row>
     <row r="88" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A88" s="96"/>
-      <c r="B88" s="98"/>
-      <c r="C88" s="97"/>
-      <c r="D88" s="97"/>
-      <c r="E88" s="99"/>
+      <c r="A88" s="95"/>
+      <c r="B88" s="97"/>
+      <c r="C88" s="96"/>
+      <c r="D88" s="96"/>
+      <c r="E88" s="98"/>
       <c r="F88" s="70">
         <v>2</v>
       </c>
       <c r="G88" s="72"/>
       <c r="H88" s="73"/>
-      <c r="I88" s="91"/>
+      <c r="I88" s="90"/>
       <c r="J88" s="73"/>
-      <c r="K88" s="84"/>
+      <c r="K88" s="103"/>
       <c r="L88" s="71"/>
     </row>
     <row r="89" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A89" s="96"/>
-      <c r="B89" s="98"/>
-      <c r="C89" s="97"/>
-      <c r="D89" s="97"/>
-      <c r="E89" s="99"/>
+      <c r="A89" s="95"/>
+      <c r="B89" s="97"/>
+      <c r="C89" s="96"/>
+      <c r="D89" s="96"/>
+      <c r="E89" s="98"/>
       <c r="F89" s="70">
         <v>3</v>
       </c>
       <c r="G89" s="72"/>
       <c r="H89" s="73"/>
-      <c r="I89" s="91"/>
+      <c r="I89" s="90"/>
       <c r="J89" s="73"/>
-      <c r="K89" s="84"/>
+      <c r="K89" s="103"/>
       <c r="L89" s="71"/>
     </row>
     <row r="90" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A90" s="96"/>
-      <c r="B90" s="98"/>
-      <c r="C90" s="97"/>
-      <c r="D90" s="97"/>
-      <c r="E90" s="99"/>
+      <c r="A90" s="95"/>
+      <c r="B90" s="97"/>
+      <c r="C90" s="96"/>
+      <c r="D90" s="96"/>
+      <c r="E90" s="98"/>
       <c r="F90" s="70">
         <v>4</v>
       </c>
       <c r="G90" s="72"/>
       <c r="H90" s="73"/>
-      <c r="I90" s="91"/>
+      <c r="I90" s="90"/>
       <c r="J90" s="73"/>
-      <c r="K90" s="84"/>
+      <c r="K90" s="103"/>
       <c r="L90" s="71"/>
     </row>
     <row r="91" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A91" s="96"/>
-      <c r="B91" s="98"/>
-      <c r="C91" s="97"/>
-      <c r="D91" s="97"/>
-      <c r="E91" s="99"/>
+      <c r="A91" s="95"/>
+      <c r="B91" s="97"/>
+      <c r="C91" s="96"/>
+      <c r="D91" s="96"/>
+      <c r="E91" s="98"/>
       <c r="F91" s="70">
         <v>5</v>
       </c>
       <c r="G91" s="72"/>
       <c r="H91" s="73"/>
-      <c r="I91" s="91"/>
+      <c r="I91" s="90"/>
       <c r="J91" s="73"/>
-      <c r="K91" s="84"/>
+      <c r="K91" s="104"/>
       <c r="L91" s="71"/>
     </row>
     <row r="92" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A92" s="92">
+      <c r="A92" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(19,Registro!$T$2:$T$100,0))="","", 19),"")</f>
         <v>19</v>
       </c>
-      <c r="B92" s="93" t="str">
+      <c r="B92" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(19,Registro!$T$2:$T$100,0)),"")</f>
         <v>1012383996</v>
       </c>
-      <c r="C92" s="93" t="str">
+      <c r="C92" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(19,Registro!$T$2:$T$100,0)),"")</f>
         <v>Haidivy Lorena Orosco Viracacha</v>
       </c>
-      <c r="D92" s="93" t="str">
+      <c r="D92" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(19,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E92" s="95">
+      <c r="E92" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(19,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -16205,93 +16239,93 @@
       </c>
       <c r="G92" s="68"/>
       <c r="H92" s="69"/>
-      <c r="I92" s="90"/>
+      <c r="I92" s="89"/>
       <c r="J92" s="69"/>
-      <c r="K92" s="66"/>
+      <c r="K92" s="99"/>
       <c r="L92" s="67"/>
     </row>
     <row r="93" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A93" s="92"/>
-      <c r="B93" s="94"/>
-      <c r="C93" s="93"/>
-      <c r="D93" s="93"/>
-      <c r="E93" s="95"/>
+      <c r="A93" s="91"/>
+      <c r="B93" s="93"/>
+      <c r="C93" s="92"/>
+      <c r="D93" s="92"/>
+      <c r="E93" s="94"/>
       <c r="F93" s="66">
         <v>2</v>
       </c>
       <c r="G93" s="68"/>
       <c r="H93" s="69"/>
-      <c r="I93" s="90"/>
+      <c r="I93" s="89"/>
       <c r="J93" s="69"/>
-      <c r="K93" s="66"/>
+      <c r="K93" s="100"/>
       <c r="L93" s="67"/>
     </row>
     <row r="94" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A94" s="92"/>
-      <c r="B94" s="94"/>
-      <c r="C94" s="93"/>
-      <c r="D94" s="93"/>
-      <c r="E94" s="95"/>
+      <c r="A94" s="91"/>
+      <c r="B94" s="93"/>
+      <c r="C94" s="92"/>
+      <c r="D94" s="92"/>
+      <c r="E94" s="94"/>
       <c r="F94" s="66">
         <v>3</v>
       </c>
       <c r="G94" s="68"/>
       <c r="H94" s="69"/>
-      <c r="I94" s="90"/>
+      <c r="I94" s="89"/>
       <c r="J94" s="69"/>
-      <c r="K94" s="66"/>
+      <c r="K94" s="100"/>
       <c r="L94" s="67"/>
     </row>
     <row r="95" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A95" s="92"/>
-      <c r="B95" s="94"/>
-      <c r="C95" s="93"/>
-      <c r="D95" s="93"/>
-      <c r="E95" s="95"/>
+      <c r="A95" s="91"/>
+      <c r="B95" s="93"/>
+      <c r="C95" s="92"/>
+      <c r="D95" s="92"/>
+      <c r="E95" s="94"/>
       <c r="F95" s="66">
         <v>4</v>
       </c>
       <c r="G95" s="68"/>
       <c r="H95" s="69"/>
-      <c r="I95" s="90"/>
+      <c r="I95" s="89"/>
       <c r="J95" s="69"/>
-      <c r="K95" s="66"/>
+      <c r="K95" s="100"/>
       <c r="L95" s="67"/>
     </row>
     <row r="96" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A96" s="92"/>
-      <c r="B96" s="94"/>
-      <c r="C96" s="93"/>
-      <c r="D96" s="93"/>
-      <c r="E96" s="95"/>
+      <c r="A96" s="91"/>
+      <c r="B96" s="93"/>
+      <c r="C96" s="92"/>
+      <c r="D96" s="92"/>
+      <c r="E96" s="94"/>
       <c r="F96" s="66">
         <v>5</v>
       </c>
       <c r="G96" s="68"/>
       <c r="H96" s="69"/>
-      <c r="I96" s="90"/>
+      <c r="I96" s="89"/>
       <c r="J96" s="69"/>
-      <c r="K96" s="66"/>
+      <c r="K96" s="101"/>
       <c r="L96" s="67"/>
     </row>
     <row r="97" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A97" s="96">
+      <c r="A97" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(20,Registro!$T$2:$T$100,0))="","", 20),"")</f>
         <v>20</v>
       </c>
-      <c r="B97" s="97" t="str">
+      <c r="B97" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(20,Registro!$T$2:$T$100,0)),"")</f>
         <v>1012390029</v>
       </c>
-      <c r="C97" s="97" t="str">
+      <c r="C97" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(20,Registro!$T$2:$T$100,0)),"")</f>
         <v>Luisa Maria Hormaza Hernández</v>
       </c>
-      <c r="D97" s="97" t="str">
+      <c r="D97" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(20,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E97" s="99">
+      <c r="E97" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(20,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -16300,93 +16334,93 @@
       </c>
       <c r="G97" s="72"/>
       <c r="H97" s="73"/>
-      <c r="I97" s="91"/>
+      <c r="I97" s="90"/>
       <c r="J97" s="73"/>
-      <c r="K97" s="84"/>
+      <c r="K97" s="102"/>
       <c r="L97" s="71"/>
     </row>
     <row r="98" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A98" s="96"/>
-      <c r="B98" s="98"/>
-      <c r="C98" s="97"/>
-      <c r="D98" s="97"/>
-      <c r="E98" s="99"/>
+      <c r="A98" s="95"/>
+      <c r="B98" s="97"/>
+      <c r="C98" s="96"/>
+      <c r="D98" s="96"/>
+      <c r="E98" s="98"/>
       <c r="F98" s="70">
         <v>2</v>
       </c>
       <c r="G98" s="72"/>
       <c r="H98" s="73"/>
-      <c r="I98" s="91"/>
+      <c r="I98" s="90"/>
       <c r="J98" s="73"/>
-      <c r="K98" s="84"/>
+      <c r="K98" s="103"/>
       <c r="L98" s="71"/>
     </row>
     <row r="99" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A99" s="96"/>
-      <c r="B99" s="98"/>
-      <c r="C99" s="97"/>
-      <c r="D99" s="97"/>
-      <c r="E99" s="99"/>
+      <c r="A99" s="95"/>
+      <c r="B99" s="97"/>
+      <c r="C99" s="96"/>
+      <c r="D99" s="96"/>
+      <c r="E99" s="98"/>
       <c r="F99" s="70">
         <v>3</v>
       </c>
       <c r="G99" s="72"/>
       <c r="H99" s="73"/>
-      <c r="I99" s="91"/>
+      <c r="I99" s="90"/>
       <c r="J99" s="73"/>
-      <c r="K99" s="84"/>
+      <c r="K99" s="103"/>
       <c r="L99" s="71"/>
     </row>
     <row r="100" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A100" s="96"/>
-      <c r="B100" s="98"/>
-      <c r="C100" s="97"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="99"/>
+      <c r="A100" s="95"/>
+      <c r="B100" s="97"/>
+      <c r="C100" s="96"/>
+      <c r="D100" s="96"/>
+      <c r="E100" s="98"/>
       <c r="F100" s="70">
         <v>4</v>
       </c>
       <c r="G100" s="72"/>
       <c r="H100" s="73"/>
-      <c r="I100" s="91"/>
+      <c r="I100" s="90"/>
       <c r="J100" s="73"/>
-      <c r="K100" s="84"/>
+      <c r="K100" s="103"/>
       <c r="L100" s="71"/>
     </row>
     <row r="101" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A101" s="96"/>
-      <c r="B101" s="98"/>
-      <c r="C101" s="97"/>
-      <c r="D101" s="97"/>
-      <c r="E101" s="99"/>
+      <c r="A101" s="95"/>
+      <c r="B101" s="97"/>
+      <c r="C101" s="96"/>
+      <c r="D101" s="96"/>
+      <c r="E101" s="98"/>
       <c r="F101" s="70">
         <v>5</v>
       </c>
       <c r="G101" s="72"/>
       <c r="H101" s="73"/>
-      <c r="I101" s="91"/>
+      <c r="I101" s="90"/>
       <c r="J101" s="73"/>
-      <c r="K101" s="84"/>
+      <c r="K101" s="104"/>
       <c r="L101" s="71"/>
     </row>
     <row r="102" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A102" s="92">
+      <c r="A102" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(21,Registro!$T$2:$T$100,0))="","", 21),"")</f>
         <v>21</v>
       </c>
-      <c r="B102" s="93" t="str">
+      <c r="B102" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(21,Registro!$T$2:$T$100,0)),"")</f>
         <v>1012411807</v>
       </c>
-      <c r="C102" s="93" t="str">
+      <c r="C102" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(21,Registro!$T$2:$T$100,0)),"")</f>
         <v>Juan Camilo Álvarez Muñoz</v>
       </c>
-      <c r="D102" s="93" t="str">
+      <c r="D102" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(21,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E102" s="95">
+      <c r="E102" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(21,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -16395,93 +16429,93 @@
       </c>
       <c r="G102" s="68"/>
       <c r="H102" s="69"/>
-      <c r="I102" s="90"/>
+      <c r="I102" s="89"/>
       <c r="J102" s="69"/>
-      <c r="K102" s="66"/>
+      <c r="K102" s="99"/>
       <c r="L102" s="67"/>
     </row>
     <row r="103" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A103" s="92"/>
-      <c r="B103" s="94"/>
-      <c r="C103" s="93"/>
-      <c r="D103" s="93"/>
-      <c r="E103" s="95"/>
+      <c r="A103" s="91"/>
+      <c r="B103" s="93"/>
+      <c r="C103" s="92"/>
+      <c r="D103" s="92"/>
+      <c r="E103" s="94"/>
       <c r="F103" s="66">
         <v>2</v>
       </c>
       <c r="G103" s="68"/>
       <c r="H103" s="69"/>
-      <c r="I103" s="90"/>
+      <c r="I103" s="89"/>
       <c r="J103" s="69"/>
-      <c r="K103" s="66"/>
+      <c r="K103" s="100"/>
       <c r="L103" s="67"/>
     </row>
     <row r="104" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A104" s="92"/>
-      <c r="B104" s="94"/>
-      <c r="C104" s="93"/>
-      <c r="D104" s="93"/>
-      <c r="E104" s="95"/>
+      <c r="A104" s="91"/>
+      <c r="B104" s="93"/>
+      <c r="C104" s="92"/>
+      <c r="D104" s="92"/>
+      <c r="E104" s="94"/>
       <c r="F104" s="66">
         <v>3</v>
       </c>
       <c r="G104" s="68"/>
       <c r="H104" s="69"/>
-      <c r="I104" s="90"/>
+      <c r="I104" s="89"/>
       <c r="J104" s="69"/>
-      <c r="K104" s="66"/>
+      <c r="K104" s="100"/>
       <c r="L104" s="67"/>
     </row>
     <row r="105" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A105" s="92"/>
-      <c r="B105" s="94"/>
-      <c r="C105" s="93"/>
-      <c r="D105" s="93"/>
-      <c r="E105" s="95"/>
+      <c r="A105" s="91"/>
+      <c r="B105" s="93"/>
+      <c r="C105" s="92"/>
+      <c r="D105" s="92"/>
+      <c r="E105" s="94"/>
       <c r="F105" s="66">
         <v>4</v>
       </c>
       <c r="G105" s="68"/>
       <c r="H105" s="69"/>
-      <c r="I105" s="90"/>
+      <c r="I105" s="89"/>
       <c r="J105" s="69"/>
-      <c r="K105" s="66"/>
+      <c r="K105" s="100"/>
       <c r="L105" s="67"/>
     </row>
     <row r="106" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A106" s="92"/>
-      <c r="B106" s="94"/>
-      <c r="C106" s="93"/>
-      <c r="D106" s="93"/>
-      <c r="E106" s="95"/>
+      <c r="A106" s="91"/>
+      <c r="B106" s="93"/>
+      <c r="C106" s="92"/>
+      <c r="D106" s="92"/>
+      <c r="E106" s="94"/>
       <c r="F106" s="66">
         <v>5</v>
       </c>
       <c r="G106" s="68"/>
       <c r="H106" s="69"/>
-      <c r="I106" s="90"/>
+      <c r="I106" s="89"/>
       <c r="J106" s="69"/>
-      <c r="K106" s="66"/>
+      <c r="K106" s="101"/>
       <c r="L106" s="67"/>
     </row>
     <row r="107" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A107" s="96">
+      <c r="A107" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(22,Registro!$T$2:$T$100,0))="","", 22),"")</f>
         <v>22</v>
       </c>
-      <c r="B107" s="97" t="str">
+      <c r="B107" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(22,Registro!$T$2:$T$100,0)),"")</f>
         <v>1018453638</v>
       </c>
-      <c r="C107" s="97" t="str">
+      <c r="C107" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(22,Registro!$T$2:$T$100,0)),"")</f>
         <v>Andes Leonardo Martínez Bejarano</v>
       </c>
-      <c r="D107" s="97" t="str">
+      <c r="D107" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(22,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E107" s="99">
+      <c r="E107" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(22,Registro!$T$2:$T$100,0)),"")</f>
         <v>71</v>
       </c>
@@ -16490,93 +16524,93 @@
       </c>
       <c r="G107" s="72"/>
       <c r="H107" s="73"/>
-      <c r="I107" s="91"/>
+      <c r="I107" s="90"/>
       <c r="J107" s="73"/>
-      <c r="K107" s="84"/>
+      <c r="K107" s="102"/>
       <c r="L107" s="71"/>
     </row>
     <row r="108" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A108" s="96"/>
-      <c r="B108" s="98"/>
-      <c r="C108" s="97"/>
-      <c r="D108" s="97"/>
-      <c r="E108" s="99"/>
+      <c r="A108" s="95"/>
+      <c r="B108" s="97"/>
+      <c r="C108" s="96"/>
+      <c r="D108" s="96"/>
+      <c r="E108" s="98"/>
       <c r="F108" s="70">
         <v>2</v>
       </c>
       <c r="G108" s="72"/>
       <c r="H108" s="73"/>
-      <c r="I108" s="91"/>
+      <c r="I108" s="90"/>
       <c r="J108" s="73"/>
-      <c r="K108" s="84"/>
+      <c r="K108" s="103"/>
       <c r="L108" s="71"/>
     </row>
     <row r="109" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A109" s="96"/>
-      <c r="B109" s="98"/>
-      <c r="C109" s="97"/>
-      <c r="D109" s="97"/>
-      <c r="E109" s="99"/>
+      <c r="A109" s="95"/>
+      <c r="B109" s="97"/>
+      <c r="C109" s="96"/>
+      <c r="D109" s="96"/>
+      <c r="E109" s="98"/>
       <c r="F109" s="70">
         <v>3</v>
       </c>
       <c r="G109" s="72"/>
       <c r="H109" s="73"/>
-      <c r="I109" s="91"/>
+      <c r="I109" s="90"/>
       <c r="J109" s="73"/>
-      <c r="K109" s="84"/>
+      <c r="K109" s="103"/>
       <c r="L109" s="71"/>
     </row>
     <row r="110" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A110" s="96"/>
-      <c r="B110" s="98"/>
-      <c r="C110" s="97"/>
-      <c r="D110" s="97"/>
-      <c r="E110" s="99"/>
+      <c r="A110" s="95"/>
+      <c r="B110" s="97"/>
+      <c r="C110" s="96"/>
+      <c r="D110" s="96"/>
+      <c r="E110" s="98"/>
       <c r="F110" s="70">
         <v>4</v>
       </c>
       <c r="G110" s="72"/>
       <c r="H110" s="73"/>
-      <c r="I110" s="91"/>
+      <c r="I110" s="90"/>
       <c r="J110" s="73"/>
-      <c r="K110" s="84"/>
+      <c r="K110" s="103"/>
       <c r="L110" s="71"/>
     </row>
     <row r="111" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A111" s="96"/>
-      <c r="B111" s="98"/>
-      <c r="C111" s="97"/>
-      <c r="D111" s="97"/>
-      <c r="E111" s="99"/>
+      <c r="A111" s="95"/>
+      <c r="B111" s="97"/>
+      <c r="C111" s="96"/>
+      <c r="D111" s="96"/>
+      <c r="E111" s="98"/>
       <c r="F111" s="70">
         <v>5</v>
       </c>
       <c r="G111" s="72"/>
       <c r="H111" s="73"/>
-      <c r="I111" s="91"/>
+      <c r="I111" s="90"/>
       <c r="J111" s="73"/>
-      <c r="K111" s="84"/>
+      <c r="K111" s="104"/>
       <c r="L111" s="71"/>
     </row>
     <row r="112" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A112" s="92">
+      <c r="A112" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(23,Registro!$T$2:$T$100,0))="","", 23),"")</f>
         <v>23</v>
       </c>
-      <c r="B112" s="93" t="str">
+      <c r="B112" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(23,Registro!$T$2:$T$100,0)),"")</f>
         <v>1000805475</v>
       </c>
-      <c r="C112" s="93" t="str">
+      <c r="C112" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(23,Registro!$T$2:$T$100,0)),"")</f>
         <v>Wendy Carolina Cortes Rincón</v>
       </c>
-      <c r="D112" s="93" t="str">
+      <c r="D112" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(23,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E112" s="95">
+      <c r="E112" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(23,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -16585,93 +16619,93 @@
       </c>
       <c r="G112" s="68"/>
       <c r="H112" s="69"/>
-      <c r="I112" s="90"/>
+      <c r="I112" s="89"/>
       <c r="J112" s="69"/>
-      <c r="K112" s="66"/>
+      <c r="K112" s="99"/>
       <c r="L112" s="67"/>
     </row>
     <row r="113" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A113" s="92"/>
-      <c r="B113" s="94"/>
-      <c r="C113" s="93"/>
-      <c r="D113" s="93"/>
-      <c r="E113" s="95"/>
+      <c r="A113" s="91"/>
+      <c r="B113" s="93"/>
+      <c r="C113" s="92"/>
+      <c r="D113" s="92"/>
+      <c r="E113" s="94"/>
       <c r="F113" s="66">
         <v>2</v>
       </c>
       <c r="G113" s="68"/>
       <c r="H113" s="69"/>
-      <c r="I113" s="90"/>
+      <c r="I113" s="89"/>
       <c r="J113" s="69"/>
-      <c r="K113" s="66"/>
+      <c r="K113" s="100"/>
       <c r="L113" s="67"/>
     </row>
     <row r="114" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A114" s="92"/>
-      <c r="B114" s="94"/>
-      <c r="C114" s="93"/>
-      <c r="D114" s="93"/>
-      <c r="E114" s="95"/>
+      <c r="A114" s="91"/>
+      <c r="B114" s="93"/>
+      <c r="C114" s="92"/>
+      <c r="D114" s="92"/>
+      <c r="E114" s="94"/>
       <c r="F114" s="66">
         <v>3</v>
       </c>
       <c r="G114" s="68"/>
       <c r="H114" s="69"/>
-      <c r="I114" s="90"/>
+      <c r="I114" s="89"/>
       <c r="J114" s="69"/>
-      <c r="K114" s="66"/>
+      <c r="K114" s="100"/>
       <c r="L114" s="67"/>
     </row>
     <row r="115" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A115" s="92"/>
-      <c r="B115" s="94"/>
-      <c r="C115" s="93"/>
-      <c r="D115" s="93"/>
-      <c r="E115" s="95"/>
+      <c r="A115" s="91"/>
+      <c r="B115" s="93"/>
+      <c r="C115" s="92"/>
+      <c r="D115" s="92"/>
+      <c r="E115" s="94"/>
       <c r="F115" s="66">
         <v>4</v>
       </c>
       <c r="G115" s="68"/>
       <c r="H115" s="69"/>
-      <c r="I115" s="90"/>
+      <c r="I115" s="89"/>
       <c r="J115" s="69"/>
-      <c r="K115" s="66"/>
+      <c r="K115" s="100"/>
       <c r="L115" s="67"/>
     </row>
     <row r="116" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A116" s="92"/>
-      <c r="B116" s="94"/>
-      <c r="C116" s="93"/>
-      <c r="D116" s="93"/>
-      <c r="E116" s="95"/>
+      <c r="A116" s="91"/>
+      <c r="B116" s="93"/>
+      <c r="C116" s="92"/>
+      <c r="D116" s="92"/>
+      <c r="E116" s="94"/>
       <c r="F116" s="66">
         <v>5</v>
       </c>
       <c r="G116" s="68"/>
       <c r="H116" s="69"/>
-      <c r="I116" s="90"/>
+      <c r="I116" s="89"/>
       <c r="J116" s="69"/>
-      <c r="K116" s="66"/>
+      <c r="K116" s="101"/>
       <c r="L116" s="67"/>
     </row>
     <row r="117" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A117" s="96">
+      <c r="A117" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(24,Registro!$T$2:$T$100,0))="","", 24),"")</f>
         <v>24</v>
       </c>
-      <c r="B117" s="97" t="str">
+      <c r="B117" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(24,Registro!$T$2:$T$100,0)),"")</f>
         <v>3238949922</v>
       </c>
-      <c r="C117" s="97" t="str">
+      <c r="C117" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(24,Registro!$T$2:$T$100,0)),"")</f>
         <v>Cristian Johan Nuñez López</v>
       </c>
-      <c r="D117" s="97" t="str">
+      <c r="D117" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(24,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E117" s="99">
+      <c r="E117" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(24,Registro!$T$2:$T$100,0)),"")</f>
         <v>73</v>
       </c>
@@ -16680,93 +16714,93 @@
       </c>
       <c r="G117" s="72"/>
       <c r="H117" s="73"/>
-      <c r="I117" s="91"/>
+      <c r="I117" s="90"/>
       <c r="J117" s="73"/>
-      <c r="K117" s="84"/>
+      <c r="K117" s="102"/>
       <c r="L117" s="71"/>
     </row>
     <row r="118" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A118" s="96"/>
-      <c r="B118" s="98"/>
-      <c r="C118" s="97"/>
-      <c r="D118" s="97"/>
-      <c r="E118" s="99"/>
+      <c r="A118" s="95"/>
+      <c r="B118" s="97"/>
+      <c r="C118" s="96"/>
+      <c r="D118" s="96"/>
+      <c r="E118" s="98"/>
       <c r="F118" s="70">
         <v>2</v>
       </c>
       <c r="G118" s="72"/>
       <c r="H118" s="73"/>
-      <c r="I118" s="91"/>
+      <c r="I118" s="90"/>
       <c r="J118" s="73"/>
-      <c r="K118" s="84"/>
+      <c r="K118" s="103"/>
       <c r="L118" s="71"/>
     </row>
     <row r="119" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A119" s="96"/>
-      <c r="B119" s="98"/>
-      <c r="C119" s="97"/>
-      <c r="D119" s="97"/>
-      <c r="E119" s="99"/>
+      <c r="A119" s="95"/>
+      <c r="B119" s="97"/>
+      <c r="C119" s="96"/>
+      <c r="D119" s="96"/>
+      <c r="E119" s="98"/>
       <c r="F119" s="70">
         <v>3</v>
       </c>
       <c r="G119" s="72"/>
       <c r="H119" s="73"/>
-      <c r="I119" s="91"/>
+      <c r="I119" s="90"/>
       <c r="J119" s="73"/>
-      <c r="K119" s="84"/>
+      <c r="K119" s="103"/>
       <c r="L119" s="71"/>
     </row>
     <row r="120" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A120" s="96"/>
-      <c r="B120" s="98"/>
-      <c r="C120" s="97"/>
-      <c r="D120" s="97"/>
-      <c r="E120" s="99"/>
+      <c r="A120" s="95"/>
+      <c r="B120" s="97"/>
+      <c r="C120" s="96"/>
+      <c r="D120" s="96"/>
+      <c r="E120" s="98"/>
       <c r="F120" s="70">
         <v>4</v>
       </c>
       <c r="G120" s="72"/>
       <c r="H120" s="73"/>
-      <c r="I120" s="91"/>
+      <c r="I120" s="90"/>
       <c r="J120" s="73"/>
-      <c r="K120" s="84"/>
+      <c r="K120" s="103"/>
       <c r="L120" s="71"/>
     </row>
     <row r="121" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A121" s="96"/>
-      <c r="B121" s="98"/>
-      <c r="C121" s="97"/>
-      <c r="D121" s="97"/>
-      <c r="E121" s="99"/>
+      <c r="A121" s="95"/>
+      <c r="B121" s="97"/>
+      <c r="C121" s="96"/>
+      <c r="D121" s="96"/>
+      <c r="E121" s="98"/>
       <c r="F121" s="70">
         <v>5</v>
       </c>
       <c r="G121" s="72"/>
       <c r="H121" s="73"/>
-      <c r="I121" s="91"/>
+      <c r="I121" s="90"/>
       <c r="J121" s="73"/>
-      <c r="K121" s="84"/>
+      <c r="K121" s="104"/>
       <c r="L121" s="71"/>
     </row>
     <row r="122" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A122" s="92">
+      <c r="A122" s="91">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(25,Registro!$T$2:$T$100,0))="","", 25),"")</f>
         <v>25</v>
       </c>
-      <c r="B122" s="93" t="str">
+      <c r="B122" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(25,Registro!$T$2:$T$100,0)),"")</f>
         <v>1018465015</v>
       </c>
-      <c r="C122" s="93" t="str">
+      <c r="C122" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(25,Registro!$T$2:$T$100,0)),"")</f>
         <v>Geraldine Arango Robayo</v>
       </c>
-      <c r="D122" s="93" t="str">
+      <c r="D122" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(25,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E122" s="95">
+      <c r="E122" s="94">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(25,Registro!$T$2:$T$100,0)),"")</f>
         <v>71</v>
       </c>
@@ -16775,93 +16809,93 @@
       </c>
       <c r="G122" s="68"/>
       <c r="H122" s="69"/>
-      <c r="I122" s="90"/>
+      <c r="I122" s="89"/>
       <c r="J122" s="69"/>
-      <c r="K122" s="66"/>
+      <c r="K122" s="99"/>
       <c r="L122" s="67"/>
     </row>
     <row r="123" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A123" s="92"/>
-      <c r="B123" s="94"/>
-      <c r="C123" s="93"/>
-      <c r="D123" s="93"/>
-      <c r="E123" s="95"/>
+      <c r="A123" s="91"/>
+      <c r="B123" s="93"/>
+      <c r="C123" s="92"/>
+      <c r="D123" s="92"/>
+      <c r="E123" s="94"/>
       <c r="F123" s="66">
         <v>2</v>
       </c>
       <c r="G123" s="68"/>
       <c r="H123" s="69"/>
-      <c r="I123" s="90"/>
+      <c r="I123" s="89"/>
       <c r="J123" s="69"/>
-      <c r="K123" s="66"/>
+      <c r="K123" s="100"/>
       <c r="L123" s="67"/>
     </row>
     <row r="124" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A124" s="92"/>
-      <c r="B124" s="94"/>
-      <c r="C124" s="93"/>
-      <c r="D124" s="93"/>
-      <c r="E124" s="95"/>
+      <c r="A124" s="91"/>
+      <c r="B124" s="93"/>
+      <c r="C124" s="92"/>
+      <c r="D124" s="92"/>
+      <c r="E124" s="94"/>
       <c r="F124" s="66">
         <v>3</v>
       </c>
       <c r="G124" s="68"/>
       <c r="H124" s="69"/>
-      <c r="I124" s="90"/>
+      <c r="I124" s="89"/>
       <c r="J124" s="69"/>
-      <c r="K124" s="66"/>
+      <c r="K124" s="100"/>
       <c r="L124" s="67"/>
     </row>
     <row r="125" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A125" s="92"/>
-      <c r="B125" s="94"/>
-      <c r="C125" s="93"/>
-      <c r="D125" s="93"/>
-      <c r="E125" s="95"/>
+      <c r="A125" s="91"/>
+      <c r="B125" s="93"/>
+      <c r="C125" s="92"/>
+      <c r="D125" s="92"/>
+      <c r="E125" s="94"/>
       <c r="F125" s="66">
         <v>4</v>
       </c>
       <c r="G125" s="68"/>
       <c r="H125" s="69"/>
-      <c r="I125" s="90"/>
+      <c r="I125" s="89"/>
       <c r="J125" s="69"/>
-      <c r="K125" s="66"/>
+      <c r="K125" s="100"/>
       <c r="L125" s="67"/>
     </row>
     <row r="126" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A126" s="92"/>
-      <c r="B126" s="94"/>
-      <c r="C126" s="93"/>
-      <c r="D126" s="93"/>
-      <c r="E126" s="95"/>
+      <c r="A126" s="91"/>
+      <c r="B126" s="93"/>
+      <c r="C126" s="92"/>
+      <c r="D126" s="92"/>
+      <c r="E126" s="94"/>
       <c r="F126" s="66">
         <v>5</v>
       </c>
       <c r="G126" s="68"/>
       <c r="H126" s="69"/>
-      <c r="I126" s="90"/>
+      <c r="I126" s="89"/>
       <c r="J126" s="69"/>
-      <c r="K126" s="66"/>
+      <c r="K126" s="101"/>
       <c r="L126" s="67"/>
     </row>
     <row r="127" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A127" s="96">
+      <c r="A127" s="95">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(26,Registro!$T$2:$T$100,0))="","", 26),"")</f>
         <v>26</v>
       </c>
-      <c r="B127" s="97" t="str">
+      <c r="B127" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(26,Registro!$T$2:$T$100,0)),"")</f>
         <v>1000122421</v>
       </c>
-      <c r="C127" s="97" t="str">
+      <c r="C127" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(26,Registro!$T$2:$T$100,0)),"")</f>
         <v>Andrea Espitia Betancourt</v>
       </c>
-      <c r="D127" s="97" t="str">
+      <c r="D127" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(26,Registro!$T$2:$T$100,0)),"")</f>
         <v>Pregrado Virtual</v>
       </c>
-      <c r="E127" s="99">
+      <c r="E127" s="98">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(26,Registro!$T$2:$T$100,0)),"")</f>
         <v>71</v>
       </c>
@@ -16870,93 +16904,93 @@
       </c>
       <c r="G127" s="72"/>
       <c r="H127" s="73"/>
-      <c r="I127" s="91"/>
+      <c r="I127" s="90"/>
       <c r="J127" s="73"/>
-      <c r="K127" s="84"/>
+      <c r="K127" s="102"/>
       <c r="L127" s="71"/>
     </row>
     <row r="128" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A128" s="96"/>
-      <c r="B128" s="98"/>
-      <c r="C128" s="97"/>
-      <c r="D128" s="97"/>
-      <c r="E128" s="99"/>
+      <c r="A128" s="95"/>
+      <c r="B128" s="97"/>
+      <c r="C128" s="96"/>
+      <c r="D128" s="96"/>
+      <c r="E128" s="98"/>
       <c r="F128" s="70">
         <v>2</v>
       </c>
       <c r="G128" s="72"/>
       <c r="H128" s="73"/>
-      <c r="I128" s="91"/>
+      <c r="I128" s="90"/>
       <c r="J128" s="73"/>
-      <c r="K128" s="84"/>
+      <c r="K128" s="103"/>
       <c r="L128" s="71"/>
     </row>
     <row r="129" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A129" s="96"/>
-      <c r="B129" s="98"/>
-      <c r="C129" s="97"/>
-      <c r="D129" s="97"/>
-      <c r="E129" s="99"/>
+      <c r="A129" s="95"/>
+      <c r="B129" s="97"/>
+      <c r="C129" s="96"/>
+      <c r="D129" s="96"/>
+      <c r="E129" s="98"/>
       <c r="F129" s="70">
         <v>3</v>
       </c>
       <c r="G129" s="72"/>
       <c r="H129" s="73"/>
-      <c r="I129" s="91"/>
+      <c r="I129" s="90"/>
       <c r="J129" s="73"/>
-      <c r="K129" s="84"/>
+      <c r="K129" s="103"/>
       <c r="L129" s="71"/>
     </row>
     <row r="130" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A130" s="96"/>
-      <c r="B130" s="98"/>
-      <c r="C130" s="97"/>
-      <c r="D130" s="97"/>
-      <c r="E130" s="99"/>
+      <c r="A130" s="95"/>
+      <c r="B130" s="97"/>
+      <c r="C130" s="96"/>
+      <c r="D130" s="96"/>
+      <c r="E130" s="98"/>
       <c r="F130" s="70">
         <v>4</v>
       </c>
       <c r="G130" s="72"/>
       <c r="H130" s="73"/>
-      <c r="I130" s="91"/>
+      <c r="I130" s="90"/>
       <c r="J130" s="73"/>
-      <c r="K130" s="84"/>
+      <c r="K130" s="103"/>
       <c r="L130" s="71"/>
     </row>
     <row r="131" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A131" s="96"/>
-      <c r="B131" s="98"/>
-      <c r="C131" s="97"/>
-      <c r="D131" s="97"/>
-      <c r="E131" s="99"/>
+      <c r="A131" s="95"/>
+      <c r="B131" s="97"/>
+      <c r="C131" s="96"/>
+      <c r="D131" s="96"/>
+      <c r="E131" s="98"/>
       <c r="F131" s="70">
         <v>5</v>
       </c>
       <c r="G131" s="72"/>
       <c r="H131" s="73"/>
-      <c r="I131" s="91"/>
+      <c r="I131" s="90"/>
       <c r="J131" s="73"/>
-      <c r="K131" s="84"/>
+      <c r="K131" s="104"/>
       <c r="L131" s="71"/>
     </row>
     <row r="132" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A132" s="92" t="str">
+      <c r="A132" s="91" t="str">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(27,Registro!$T$2:$T$100,0))="","", 27),"")</f>
         <v/>
       </c>
-      <c r="B132" s="93" t="str">
+      <c r="B132" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(27,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="C132" s="93" t="str">
+      <c r="C132" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(27,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="D132" s="93" t="str">
+      <c r="D132" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(27,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="E132" s="95" t="str">
+      <c r="E132" s="94" t="str">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(27,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
@@ -16965,93 +16999,93 @@
       </c>
       <c r="G132" s="68"/>
       <c r="H132" s="69"/>
-      <c r="I132" s="90"/>
+      <c r="I132" s="89"/>
       <c r="J132" s="69"/>
-      <c r="K132" s="66"/>
+      <c r="K132" s="99"/>
       <c r="L132" s="67"/>
     </row>
     <row r="133" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A133" s="92"/>
-      <c r="B133" s="94"/>
-      <c r="C133" s="93"/>
-      <c r="D133" s="93"/>
-      <c r="E133" s="95"/>
+      <c r="A133" s="91"/>
+      <c r="B133" s="93"/>
+      <c r="C133" s="92"/>
+      <c r="D133" s="92"/>
+      <c r="E133" s="94"/>
       <c r="F133" s="66">
         <v>2</v>
       </c>
       <c r="G133" s="68"/>
       <c r="H133" s="69"/>
-      <c r="I133" s="90"/>
+      <c r="I133" s="89"/>
       <c r="J133" s="69"/>
-      <c r="K133" s="66"/>
+      <c r="K133" s="100"/>
       <c r="L133" s="67"/>
     </row>
     <row r="134" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A134" s="92"/>
-      <c r="B134" s="94"/>
-      <c r="C134" s="93"/>
-      <c r="D134" s="93"/>
-      <c r="E134" s="95"/>
+      <c r="A134" s="91"/>
+      <c r="B134" s="93"/>
+      <c r="C134" s="92"/>
+      <c r="D134" s="92"/>
+      <c r="E134" s="94"/>
       <c r="F134" s="66">
         <v>3</v>
       </c>
       <c r="G134" s="68"/>
       <c r="H134" s="69"/>
-      <c r="I134" s="90"/>
+      <c r="I134" s="89"/>
       <c r="J134" s="69"/>
-      <c r="K134" s="66"/>
+      <c r="K134" s="100"/>
       <c r="L134" s="67"/>
     </row>
     <row r="135" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A135" s="92"/>
-      <c r="B135" s="94"/>
-      <c r="C135" s="93"/>
-      <c r="D135" s="93"/>
-      <c r="E135" s="95"/>
+      <c r="A135" s="91"/>
+      <c r="B135" s="93"/>
+      <c r="C135" s="92"/>
+      <c r="D135" s="92"/>
+      <c r="E135" s="94"/>
       <c r="F135" s="66">
         <v>4</v>
       </c>
       <c r="G135" s="68"/>
       <c r="H135" s="69"/>
-      <c r="I135" s="90"/>
+      <c r="I135" s="89"/>
       <c r="J135" s="69"/>
-      <c r="K135" s="66"/>
+      <c r="K135" s="100"/>
       <c r="L135" s="67"/>
     </row>
     <row r="136" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A136" s="92"/>
-      <c r="B136" s="94"/>
-      <c r="C136" s="93"/>
-      <c r="D136" s="93"/>
-      <c r="E136" s="95"/>
+      <c r="A136" s="91"/>
+      <c r="B136" s="93"/>
+      <c r="C136" s="92"/>
+      <c r="D136" s="92"/>
+      <c r="E136" s="94"/>
       <c r="F136" s="66">
         <v>5</v>
       </c>
       <c r="G136" s="68"/>
       <c r="H136" s="69"/>
-      <c r="I136" s="90"/>
+      <c r="I136" s="89"/>
       <c r="J136" s="69"/>
-      <c r="K136" s="66"/>
+      <c r="K136" s="101"/>
       <c r="L136" s="67"/>
     </row>
     <row r="137" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A137" s="96" t="str">
+      <c r="A137" s="95" t="str">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(28,Registro!$T$2:$T$100,0))="","", 28),"")</f>
         <v/>
       </c>
-      <c r="B137" s="97" t="str">
+      <c r="B137" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(28,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="C137" s="97" t="str">
+      <c r="C137" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(28,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="D137" s="97" t="str">
+      <c r="D137" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(28,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="E137" s="99" t="str">
+      <c r="E137" s="98" t="str">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(28,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
@@ -17060,93 +17094,93 @@
       </c>
       <c r="G137" s="72"/>
       <c r="H137" s="73"/>
-      <c r="I137" s="91"/>
+      <c r="I137" s="90"/>
       <c r="J137" s="73"/>
-      <c r="K137" s="84"/>
+      <c r="K137" s="102"/>
       <c r="L137" s="71"/>
     </row>
     <row r="138" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A138" s="96"/>
-      <c r="B138" s="98"/>
-      <c r="C138" s="97"/>
-      <c r="D138" s="97"/>
-      <c r="E138" s="99"/>
+      <c r="A138" s="95"/>
+      <c r="B138" s="97"/>
+      <c r="C138" s="96"/>
+      <c r="D138" s="96"/>
+      <c r="E138" s="98"/>
       <c r="F138" s="70">
         <v>2</v>
       </c>
       <c r="G138" s="72"/>
       <c r="H138" s="73"/>
-      <c r="I138" s="91"/>
+      <c r="I138" s="90"/>
       <c r="J138" s="73"/>
-      <c r="K138" s="84"/>
+      <c r="K138" s="103"/>
       <c r="L138" s="71"/>
     </row>
     <row r="139" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A139" s="96"/>
-      <c r="B139" s="98"/>
-      <c r="C139" s="97"/>
-      <c r="D139" s="97"/>
-      <c r="E139" s="99"/>
+      <c r="A139" s="95"/>
+      <c r="B139" s="97"/>
+      <c r="C139" s="96"/>
+      <c r="D139" s="96"/>
+      <c r="E139" s="98"/>
       <c r="F139" s="70">
         <v>3</v>
       </c>
       <c r="G139" s="72"/>
       <c r="H139" s="73"/>
-      <c r="I139" s="91"/>
+      <c r="I139" s="90"/>
       <c r="J139" s="73"/>
-      <c r="K139" s="84"/>
+      <c r="K139" s="103"/>
       <c r="L139" s="71"/>
     </row>
     <row r="140" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A140" s="96"/>
-      <c r="B140" s="98"/>
-      <c r="C140" s="97"/>
-      <c r="D140" s="97"/>
-      <c r="E140" s="99"/>
+      <c r="A140" s="95"/>
+      <c r="B140" s="97"/>
+      <c r="C140" s="96"/>
+      <c r="D140" s="96"/>
+      <c r="E140" s="98"/>
       <c r="F140" s="70">
         <v>4</v>
       </c>
       <c r="G140" s="72"/>
       <c r="H140" s="73"/>
-      <c r="I140" s="91"/>
+      <c r="I140" s="90"/>
       <c r="J140" s="73"/>
-      <c r="K140" s="84"/>
+      <c r="K140" s="103"/>
       <c r="L140" s="71"/>
     </row>
     <row r="141" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A141" s="96"/>
-      <c r="B141" s="98"/>
-      <c r="C141" s="97"/>
-      <c r="D141" s="97"/>
-      <c r="E141" s="99"/>
+      <c r="A141" s="95"/>
+      <c r="B141" s="97"/>
+      <c r="C141" s="96"/>
+      <c r="D141" s="96"/>
+      <c r="E141" s="98"/>
       <c r="F141" s="70">
         <v>5</v>
       </c>
       <c r="G141" s="72"/>
       <c r="H141" s="73"/>
-      <c r="I141" s="91"/>
+      <c r="I141" s="90"/>
       <c r="J141" s="73"/>
-      <c r="K141" s="84"/>
+      <c r="K141" s="104"/>
       <c r="L141" s="71"/>
     </row>
     <row r="142" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A142" s="92" t="str">
+      <c r="A142" s="91" t="str">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(29,Registro!$T$2:$T$100,0))="","", 29),"")</f>
         <v/>
       </c>
-      <c r="B142" s="93" t="str">
+      <c r="B142" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(29,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="C142" s="93" t="str">
+      <c r="C142" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(29,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="D142" s="93" t="str">
+      <c r="D142" s="92" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(29,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="E142" s="95" t="str">
+      <c r="E142" s="94" t="str">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(29,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
@@ -17155,93 +17189,93 @@
       </c>
       <c r="G142" s="68"/>
       <c r="H142" s="69"/>
-      <c r="I142" s="90"/>
+      <c r="I142" s="89"/>
       <c r="J142" s="69"/>
-      <c r="K142" s="66"/>
+      <c r="K142" s="99"/>
       <c r="L142" s="67"/>
     </row>
     <row r="143" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A143" s="92"/>
-      <c r="B143" s="94"/>
-      <c r="C143" s="93"/>
-      <c r="D143" s="93"/>
-      <c r="E143" s="95"/>
+      <c r="A143" s="91"/>
+      <c r="B143" s="93"/>
+      <c r="C143" s="92"/>
+      <c r="D143" s="92"/>
+      <c r="E143" s="94"/>
       <c r="F143" s="66">
         <v>2</v>
       </c>
       <c r="G143" s="68"/>
       <c r="H143" s="69"/>
-      <c r="I143" s="90"/>
+      <c r="I143" s="89"/>
       <c r="J143" s="69"/>
-      <c r="K143" s="66"/>
+      <c r="K143" s="100"/>
       <c r="L143" s="67"/>
     </row>
     <row r="144" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A144" s="92"/>
-      <c r="B144" s="94"/>
-      <c r="C144" s="93"/>
-      <c r="D144" s="93"/>
-      <c r="E144" s="95"/>
+      <c r="A144" s="91"/>
+      <c r="B144" s="93"/>
+      <c r="C144" s="92"/>
+      <c r="D144" s="92"/>
+      <c r="E144" s="94"/>
       <c r="F144" s="66">
         <v>3</v>
       </c>
       <c r="G144" s="68"/>
       <c r="H144" s="69"/>
-      <c r="I144" s="90"/>
+      <c r="I144" s="89"/>
       <c r="J144" s="69"/>
-      <c r="K144" s="66"/>
+      <c r="K144" s="100"/>
       <c r="L144" s="67"/>
     </row>
     <row r="145" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A145" s="92"/>
-      <c r="B145" s="94"/>
-      <c r="C145" s="93"/>
-      <c r="D145" s="93"/>
-      <c r="E145" s="95"/>
+      <c r="A145" s="91"/>
+      <c r="B145" s="93"/>
+      <c r="C145" s="92"/>
+      <c r="D145" s="92"/>
+      <c r="E145" s="94"/>
       <c r="F145" s="66">
         <v>4</v>
       </c>
       <c r="G145" s="68"/>
       <c r="H145" s="69"/>
-      <c r="I145" s="90"/>
+      <c r="I145" s="89"/>
       <c r="J145" s="69"/>
-      <c r="K145" s="66"/>
+      <c r="K145" s="100"/>
       <c r="L145" s="67"/>
     </row>
     <row r="146" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A146" s="92"/>
-      <c r="B146" s="94"/>
-      <c r="C146" s="93"/>
-      <c r="D146" s="93"/>
-      <c r="E146" s="95"/>
+      <c r="A146" s="91"/>
+      <c r="B146" s="93"/>
+      <c r="C146" s="92"/>
+      <c r="D146" s="92"/>
+      <c r="E146" s="94"/>
       <c r="F146" s="66">
         <v>5</v>
       </c>
       <c r="G146" s="68"/>
       <c r="H146" s="69"/>
-      <c r="I146" s="90"/>
+      <c r="I146" s="89"/>
       <c r="J146" s="69"/>
-      <c r="K146" s="66"/>
+      <c r="K146" s="101"/>
       <c r="L146" s="67"/>
     </row>
     <row r="147" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A147" s="96" t="str">
+      <c r="A147" s="95" t="str">
         <f>IFERROR(IF(INDEX(Registro!$E$2:$E$100,MATCH(30,Registro!$T$2:$T$100,0))="","", 30),"")</f>
         <v/>
       </c>
-      <c r="B147" s="97" t="str">
+      <c r="B147" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$E$2:$E$100,MATCH(30,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="C147" s="97" t="str">
+      <c r="C147" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$F$2:$F$100,MATCH(30,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="D147" s="97" t="str">
+      <c r="D147" s="96" t="str">
         <f>IFERROR(INDEX(Registro!$B$2:$B$100,MATCH(30,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
-      <c r="E147" s="99" t="str">
+      <c r="E147" s="98" t="str">
         <f>IFERROR(INDEX(Registro!$P$2:$P$100,MATCH(30,Registro!$T$2:$T$100,0)),"")</f>
         <v/>
       </c>
@@ -17250,84 +17284,84 @@
       </c>
       <c r="G147" s="72"/>
       <c r="H147" s="73"/>
-      <c r="I147" s="91"/>
+      <c r="I147" s="90"/>
       <c r="J147" s="73"/>
-      <c r="K147" s="84"/>
+      <c r="K147" s="102"/>
       <c r="L147" s="71"/>
     </row>
     <row r="148" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A148" s="96"/>
-      <c r="B148" s="98"/>
-      <c r="C148" s="97"/>
-      <c r="D148" s="97"/>
-      <c r="E148" s="99"/>
+      <c r="A148" s="95"/>
+      <c r="B148" s="97"/>
+      <c r="C148" s="96"/>
+      <c r="D148" s="96"/>
+      <c r="E148" s="98"/>
       <c r="F148" s="70">
         <v>2</v>
       </c>
       <c r="G148" s="72"/>
       <c r="H148" s="73"/>
-      <c r="I148" s="91"/>
+      <c r="I148" s="90"/>
       <c r="J148" s="73"/>
-      <c r="K148" s="84"/>
+      <c r="K148" s="103"/>
       <c r="L148" s="71"/>
     </row>
     <row r="149" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A149" s="96"/>
-      <c r="B149" s="98"/>
-      <c r="C149" s="97"/>
-      <c r="D149" s="97"/>
-      <c r="E149" s="99"/>
+      <c r="A149" s="95"/>
+      <c r="B149" s="97"/>
+      <c r="C149" s="96"/>
+      <c r="D149" s="96"/>
+      <c r="E149" s="98"/>
       <c r="F149" s="70">
         <v>3</v>
       </c>
       <c r="G149" s="72"/>
       <c r="H149" s="73"/>
-      <c r="I149" s="91"/>
+      <c r="I149" s="90"/>
       <c r="J149" s="73"/>
-      <c r="K149" s="84"/>
+      <c r="K149" s="103"/>
       <c r="L149" s="71"/>
     </row>
     <row r="150" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A150" s="96"/>
-      <c r="B150" s="98"/>
-      <c r="C150" s="97"/>
-      <c r="D150" s="97"/>
-      <c r="E150" s="99"/>
+      <c r="A150" s="95"/>
+      <c r="B150" s="97"/>
+      <c r="C150" s="96"/>
+      <c r="D150" s="96"/>
+      <c r="E150" s="98"/>
       <c r="F150" s="70">
         <v>4</v>
       </c>
       <c r="G150" s="72"/>
       <c r="H150" s="73"/>
-      <c r="I150" s="91"/>
+      <c r="I150" s="90"/>
       <c r="J150" s="73"/>
-      <c r="K150" s="84"/>
+      <c r="K150" s="103"/>
       <c r="L150" s="71"/>
     </row>
     <row r="151" spans="1:12" ht="13.35" customHeight="1">
-      <c r="A151" s="96"/>
-      <c r="B151" s="98"/>
-      <c r="C151" s="97"/>
-      <c r="D151" s="97"/>
-      <c r="E151" s="99"/>
+      <c r="A151" s="95"/>
+      <c r="B151" s="97"/>
+      <c r="C151" s="96"/>
+      <c r="D151" s="96"/>
+      <c r="E151" s="98"/>
       <c r="F151" s="70">
         <v>5</v>
       </c>
       <c r="G151" s="72"/>
       <c r="H151" s="73"/>
-      <c r="I151" s="91"/>
+      <c r="I151" s="90"/>
       <c r="J151" s="73"/>
-      <c r="K151" s="84"/>
+      <c r="K151" s="104"/>
       <c r="L151" s="71"/>
     </row>
     <row r="152" spans="1:12">
-      <c r="E152" s="85"/>
+      <c r="E152" s="84"/>
     </row>
     <row r="153" spans="1:12" ht="15.75">
       <c r="A153" s="76"/>
       <c r="B153" s="76"/>
       <c r="C153" s="76"/>
       <c r="D153" s="76"/>
-      <c r="E153" s="86"/>
+      <c r="E153" s="85"/>
       <c r="F153" s="76"/>
       <c r="G153" s="76"/>
       <c r="H153" s="76"/>
@@ -17353,7 +17387,7 @@
       <c r="B155" s="80"/>
       <c r="C155" s="81"/>
       <c r="D155" s="81"/>
-      <c r="E155" s="87"/>
+      <c r="E155" s="86"/>
       <c r="F155" s="79"/>
       <c r="G155" s="79"/>
       <c r="H155" s="82"/>
@@ -17366,7 +17400,7 @@
       <c r="B156" s="80"/>
       <c r="C156" s="81"/>
       <c r="D156" s="81"/>
-      <c r="E156" s="87"/>
+      <c r="E156" s="86"/>
       <c r="F156" s="79"/>
       <c r="G156" s="79"/>
       <c r="H156" s="82"/>
@@ -17379,7 +17413,7 @@
       <c r="B157" s="80"/>
       <c r="C157" s="81"/>
       <c r="D157" s="81"/>
-      <c r="E157" s="87"/>
+      <c r="E157" s="86"/>
       <c r="F157" s="79"/>
       <c r="G157" s="79"/>
       <c r="H157" s="82"/>
@@ -17392,7 +17426,7 @@
       <c r="B158" s="80"/>
       <c r="C158" s="81"/>
       <c r="D158" s="81"/>
-      <c r="E158" s="87"/>
+      <c r="E158" s="86"/>
       <c r="F158" s="79"/>
       <c r="G158" s="79"/>
       <c r="H158" s="82"/>
@@ -17405,7 +17439,7 @@
       <c r="B159" s="80"/>
       <c r="C159" s="81"/>
       <c r="D159" s="81"/>
-      <c r="E159" s="87"/>
+      <c r="E159" s="86"/>
       <c r="F159" s="79"/>
       <c r="G159" s="79"/>
       <c r="H159" s="82"/>
@@ -17418,7 +17452,7 @@
       <c r="B160" s="80"/>
       <c r="C160" s="81"/>
       <c r="D160" s="81"/>
-      <c r="E160" s="87"/>
+      <c r="E160" s="86"/>
       <c r="F160" s="79"/>
       <c r="G160" s="79"/>
       <c r="H160" s="82"/>
@@ -17431,7 +17465,7 @@
       <c r="B161" s="80"/>
       <c r="C161" s="81"/>
       <c r="D161" s="81"/>
-      <c r="E161" s="87"/>
+      <c r="E161" s="86"/>
       <c r="F161" s="79"/>
       <c r="G161" s="79"/>
       <c r="H161" s="82"/>
@@ -17444,7 +17478,7 @@
       <c r="B162" s="80"/>
       <c r="C162" s="81"/>
       <c r="D162" s="81"/>
-      <c r="E162" s="87"/>
+      <c r="E162" s="86"/>
       <c r="F162" s="79"/>
       <c r="G162" s="79"/>
       <c r="H162" s="82"/>
@@ -17457,7 +17491,7 @@
       <c r="B163" s="80"/>
       <c r="C163" s="81"/>
       <c r="D163" s="81"/>
-      <c r="E163" s="87"/>
+      <c r="E163" s="86"/>
       <c r="F163" s="79"/>
       <c r="G163" s="79"/>
       <c r="H163" s="82"/>
@@ -17470,7 +17504,7 @@
       <c r="B164" s="80"/>
       <c r="C164" s="81"/>
       <c r="D164" s="81"/>
-      <c r="E164" s="87"/>
+      <c r="E164" s="86"/>
       <c r="F164" s="79"/>
       <c r="G164" s="79"/>
       <c r="H164" s="82"/>
@@ -17483,7 +17517,7 @@
       <c r="B165" s="80"/>
       <c r="C165" s="81"/>
       <c r="D165" s="81"/>
-      <c r="E165" s="87"/>
+      <c r="E165" s="86"/>
       <c r="F165" s="79"/>
       <c r="G165" s="79"/>
       <c r="H165" s="82"/>
@@ -17496,7 +17530,7 @@
       <c r="B166" s="80"/>
       <c r="C166" s="81"/>
       <c r="D166" s="81"/>
-      <c r="E166" s="87"/>
+      <c r="E166" s="86"/>
       <c r="F166" s="79"/>
       <c r="G166" s="79"/>
       <c r="H166" s="82"/>
@@ -17509,7 +17543,7 @@
       <c r="B167" s="80"/>
       <c r="C167" s="81"/>
       <c r="D167" s="81"/>
-      <c r="E167" s="87"/>
+      <c r="E167" s="86"/>
       <c r="F167" s="79"/>
       <c r="G167" s="79"/>
       <c r="H167" s="82"/>
@@ -17522,7 +17556,7 @@
       <c r="B168" s="80"/>
       <c r="C168" s="81"/>
       <c r="D168" s="81"/>
-      <c r="E168" s="87"/>
+      <c r="E168" s="86"/>
       <c r="F168" s="79"/>
       <c r="G168" s="79"/>
       <c r="H168" s="82"/>
@@ -17535,7 +17569,7 @@
       <c r="B169" s="80"/>
       <c r="C169" s="81"/>
       <c r="D169" s="81"/>
-      <c r="E169" s="87"/>
+      <c r="E169" s="86"/>
       <c r="F169" s="79"/>
       <c r="G169" s="79"/>
       <c r="H169" s="82"/>
@@ -17548,7 +17582,7 @@
       <c r="B170" s="80"/>
       <c r="C170" s="81"/>
       <c r="D170" s="81"/>
-      <c r="E170" s="87"/>
+      <c r="E170" s="86"/>
       <c r="F170" s="79"/>
       <c r="G170" s="79"/>
       <c r="H170" s="82"/>
@@ -17561,7 +17595,7 @@
       <c r="B171" s="80"/>
       <c r="C171" s="81"/>
       <c r="D171" s="81"/>
-      <c r="E171" s="87"/>
+      <c r="E171" s="86"/>
       <c r="F171" s="79"/>
       <c r="G171" s="79"/>
       <c r="H171" s="82"/>
@@ -17574,7 +17608,7 @@
       <c r="B172" s="80"/>
       <c r="C172" s="81"/>
       <c r="D172" s="81"/>
-      <c r="E172" s="87"/>
+      <c r="E172" s="86"/>
       <c r="F172" s="79"/>
       <c r="G172" s="79"/>
       <c r="H172" s="82"/>
@@ -17587,7 +17621,7 @@
       <c r="B173" s="80"/>
       <c r="C173" s="81"/>
       <c r="D173" s="81"/>
-      <c r="E173" s="87"/>
+      <c r="E173" s="86"/>
       <c r="F173" s="79"/>
       <c r="G173" s="79"/>
       <c r="H173" s="82"/>
@@ -17600,7 +17634,7 @@
       <c r="B174" s="80"/>
       <c r="C174" s="81"/>
       <c r="D174" s="81"/>
-      <c r="E174" s="87"/>
+      <c r="E174" s="86"/>
       <c r="F174" s="79"/>
       <c r="G174" s="79"/>
       <c r="H174" s="82"/>
@@ -17613,7 +17647,7 @@
       <c r="B175" s="80"/>
       <c r="C175" s="81"/>
       <c r="D175" s="81"/>
-      <c r="E175" s="87"/>
+      <c r="E175" s="86"/>
       <c r="F175" s="79"/>
       <c r="G175" s="79"/>
       <c r="H175" s="82"/>
@@ -17626,7 +17660,7 @@
       <c r="B176" s="80"/>
       <c r="C176" s="81"/>
       <c r="D176" s="81"/>
-      <c r="E176" s="87"/>
+      <c r="E176" s="86"/>
       <c r="F176" s="79"/>
       <c r="G176" s="79"/>
       <c r="H176" s="82"/>
@@ -17639,7 +17673,7 @@
       <c r="B177" s="80"/>
       <c r="C177" s="81"/>
       <c r="D177" s="81"/>
-      <c r="E177" s="87"/>
+      <c r="E177" s="86"/>
       <c r="F177" s="79"/>
       <c r="G177" s="79"/>
       <c r="H177" s="82"/>
@@ -17652,7 +17686,7 @@
       <c r="B178" s="80"/>
       <c r="C178" s="81"/>
       <c r="D178" s="81"/>
-      <c r="E178" s="87"/>
+      <c r="E178" s="86"/>
       <c r="F178" s="79"/>
       <c r="G178" s="79"/>
       <c r="H178" s="82"/>
@@ -17665,7 +17699,7 @@
       <c r="B179" s="80"/>
       <c r="C179" s="81"/>
       <c r="D179" s="81"/>
-      <c r="E179" s="87"/>
+      <c r="E179" s="86"/>
       <c r="F179" s="79"/>
       <c r="G179" s="79"/>
       <c r="H179" s="82"/>
@@ -17678,7 +17712,7 @@
       <c r="B180" s="80"/>
       <c r="C180" s="81"/>
       <c r="D180" s="81"/>
-      <c r="E180" s="87"/>
+      <c r="E180" s="86"/>
       <c r="F180" s="79"/>
       <c r="G180" s="79"/>
       <c r="H180" s="82"/>
@@ -17691,7 +17725,7 @@
       <c r="B181" s="80"/>
       <c r="C181" s="81"/>
       <c r="D181" s="81"/>
-      <c r="E181" s="87"/>
+      <c r="E181" s="86"/>
       <c r="F181" s="79"/>
       <c r="G181" s="79"/>
       <c r="H181" s="82"/>
@@ -17704,7 +17738,7 @@
       <c r="B182" s="80"/>
       <c r="C182" s="81"/>
       <c r="D182" s="81"/>
-      <c r="E182" s="87"/>
+      <c r="E182" s="86"/>
       <c r="F182" s="79"/>
       <c r="G182" s="79"/>
       <c r="H182" s="82"/>
@@ -17717,7 +17751,7 @@
       <c r="B183" s="80"/>
       <c r="C183" s="81"/>
       <c r="D183" s="81"/>
-      <c r="E183" s="87"/>
+      <c r="E183" s="86"/>
       <c r="F183" s="79"/>
       <c r="G183" s="79"/>
       <c r="H183" s="82"/>
@@ -17730,7 +17764,7 @@
       <c r="B184" s="80"/>
       <c r="C184" s="81"/>
       <c r="D184" s="81"/>
-      <c r="E184" s="87"/>
+      <c r="E184" s="86"/>
       <c r="F184" s="79"/>
       <c r="G184" s="79"/>
       <c r="H184" s="82"/>
@@ -17739,7 +17773,167 @@
       <c r="K184" s="83"/>
     </row>
   </sheetData>
-  <mergeCells count="150">
+  <mergeCells count="180">
+    <mergeCell ref="K137:K141"/>
+    <mergeCell ref="K142:K146"/>
+    <mergeCell ref="K147:K151"/>
+    <mergeCell ref="K92:K96"/>
+    <mergeCell ref="K97:K101"/>
+    <mergeCell ref="K102:K106"/>
+    <mergeCell ref="K107:K111"/>
+    <mergeCell ref="K112:K116"/>
+    <mergeCell ref="K117:K121"/>
+    <mergeCell ref="K122:K126"/>
+    <mergeCell ref="K127:K131"/>
+    <mergeCell ref="K132:K136"/>
+    <mergeCell ref="K47:K51"/>
+    <mergeCell ref="K52:K56"/>
+    <mergeCell ref="K57:K61"/>
+    <mergeCell ref="K62:K66"/>
+    <mergeCell ref="K67:K71"/>
+    <mergeCell ref="K72:K76"/>
+    <mergeCell ref="K77:K81"/>
+    <mergeCell ref="K82:K86"/>
+    <mergeCell ref="K87:K91"/>
+    <mergeCell ref="K2:K6"/>
+    <mergeCell ref="K7:K11"/>
+    <mergeCell ref="K12:K16"/>
+    <mergeCell ref="K17:K21"/>
+    <mergeCell ref="K22:K26"/>
+    <mergeCell ref="K27:K31"/>
+    <mergeCell ref="K32:K36"/>
+    <mergeCell ref="K37:K41"/>
+    <mergeCell ref="K42:K46"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="C12:C16"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="C17:C21"/>
+    <mergeCell ref="D17:D21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="C22:C26"/>
+    <mergeCell ref="D22:D26"/>
+    <mergeCell ref="E22:E26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="C27:C31"/>
+    <mergeCell ref="D27:D31"/>
+    <mergeCell ref="E27:E31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="C32:C36"/>
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="C42:C46"/>
+    <mergeCell ref="D42:D46"/>
+    <mergeCell ref="E42:E46"/>
+    <mergeCell ref="A47:A51"/>
+    <mergeCell ref="B47:B51"/>
+    <mergeCell ref="C47:C51"/>
+    <mergeCell ref="D47:D51"/>
+    <mergeCell ref="E47:E51"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="B52:B56"/>
+    <mergeCell ref="C52:C56"/>
+    <mergeCell ref="D52:D56"/>
+    <mergeCell ref="E52:E56"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="A62:A66"/>
+    <mergeCell ref="B62:B66"/>
+    <mergeCell ref="C62:C66"/>
+    <mergeCell ref="D62:D66"/>
+    <mergeCell ref="E62:E66"/>
+    <mergeCell ref="A67:A71"/>
+    <mergeCell ref="B67:B71"/>
+    <mergeCell ref="C67:C71"/>
+    <mergeCell ref="D67:D71"/>
+    <mergeCell ref="E67:E71"/>
+    <mergeCell ref="A72:A76"/>
+    <mergeCell ref="B72:B76"/>
+    <mergeCell ref="C72:C76"/>
+    <mergeCell ref="D72:D76"/>
+    <mergeCell ref="E72:E76"/>
+    <mergeCell ref="A77:A81"/>
+    <mergeCell ref="B77:B81"/>
+    <mergeCell ref="C77:C81"/>
+    <mergeCell ref="D77:D81"/>
+    <mergeCell ref="E77:E81"/>
+    <mergeCell ref="A82:A86"/>
+    <mergeCell ref="B82:B86"/>
+    <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
+    <mergeCell ref="E82:E86"/>
+    <mergeCell ref="A87:A91"/>
+    <mergeCell ref="B87:B91"/>
+    <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
+    <mergeCell ref="E87:E91"/>
+    <mergeCell ref="A92:A96"/>
+    <mergeCell ref="B92:B96"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="D92:D96"/>
+    <mergeCell ref="E92:E96"/>
+    <mergeCell ref="A97:A101"/>
+    <mergeCell ref="B97:B101"/>
+    <mergeCell ref="C97:C101"/>
+    <mergeCell ref="D97:D101"/>
+    <mergeCell ref="E97:E101"/>
+    <mergeCell ref="A102:A106"/>
+    <mergeCell ref="B102:B106"/>
+    <mergeCell ref="C102:C106"/>
+    <mergeCell ref="D102:D106"/>
+    <mergeCell ref="E102:E106"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C107:C111"/>
+    <mergeCell ref="D107:D111"/>
+    <mergeCell ref="E107:E111"/>
+    <mergeCell ref="A112:A116"/>
+    <mergeCell ref="B112:B116"/>
+    <mergeCell ref="C112:C116"/>
+    <mergeCell ref="D112:D116"/>
+    <mergeCell ref="E112:E116"/>
+    <mergeCell ref="A117:A121"/>
+    <mergeCell ref="B117:B121"/>
+    <mergeCell ref="C117:C121"/>
+    <mergeCell ref="D117:D121"/>
+    <mergeCell ref="E117:E121"/>
+    <mergeCell ref="A122:A126"/>
+    <mergeCell ref="B122:B126"/>
+    <mergeCell ref="C122:C126"/>
+    <mergeCell ref="D122:D126"/>
+    <mergeCell ref="E122:E126"/>
+    <mergeCell ref="A127:A131"/>
+    <mergeCell ref="B127:B131"/>
+    <mergeCell ref="C127:C131"/>
+    <mergeCell ref="D127:D131"/>
+    <mergeCell ref="E127:E131"/>
     <mergeCell ref="A132:A136"/>
     <mergeCell ref="B132:B136"/>
     <mergeCell ref="C132:C136"/>
@@ -17760,136 +17954,6 @@
     <mergeCell ref="C142:C146"/>
     <mergeCell ref="D142:D146"/>
     <mergeCell ref="E142:E146"/>
-    <mergeCell ref="A122:A126"/>
-    <mergeCell ref="B122:B126"/>
-    <mergeCell ref="C122:C126"/>
-    <mergeCell ref="D122:D126"/>
-    <mergeCell ref="E122:E126"/>
-    <mergeCell ref="A127:A131"/>
-    <mergeCell ref="B127:B131"/>
-    <mergeCell ref="C127:C131"/>
-    <mergeCell ref="D127:D131"/>
-    <mergeCell ref="E127:E131"/>
-    <mergeCell ref="A112:A116"/>
-    <mergeCell ref="B112:B116"/>
-    <mergeCell ref="C112:C116"/>
-    <mergeCell ref="D112:D116"/>
-    <mergeCell ref="E112:E116"/>
-    <mergeCell ref="A117:A121"/>
-    <mergeCell ref="B117:B121"/>
-    <mergeCell ref="C117:C121"/>
-    <mergeCell ref="D117:D121"/>
-    <mergeCell ref="E117:E121"/>
-    <mergeCell ref="A102:A106"/>
-    <mergeCell ref="B102:B106"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="D102:D106"/>
-    <mergeCell ref="E102:E106"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C107:C111"/>
-    <mergeCell ref="D107:D111"/>
-    <mergeCell ref="E107:E111"/>
-    <mergeCell ref="A92:A96"/>
-    <mergeCell ref="B92:B96"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="D92:D96"/>
-    <mergeCell ref="E92:E96"/>
-    <mergeCell ref="A97:A101"/>
-    <mergeCell ref="B97:B101"/>
-    <mergeCell ref="C97:C101"/>
-    <mergeCell ref="D97:D101"/>
-    <mergeCell ref="E97:E101"/>
-    <mergeCell ref="A82:A86"/>
-    <mergeCell ref="B82:B86"/>
-    <mergeCell ref="C82:C86"/>
-    <mergeCell ref="D82:D86"/>
-    <mergeCell ref="E82:E86"/>
-    <mergeCell ref="A87:A91"/>
-    <mergeCell ref="B87:B91"/>
-    <mergeCell ref="C87:C91"/>
-    <mergeCell ref="D87:D91"/>
-    <mergeCell ref="E87:E91"/>
-    <mergeCell ref="A72:A76"/>
-    <mergeCell ref="B72:B76"/>
-    <mergeCell ref="C72:C76"/>
-    <mergeCell ref="D72:D76"/>
-    <mergeCell ref="E72:E76"/>
-    <mergeCell ref="A77:A81"/>
-    <mergeCell ref="B77:B81"/>
-    <mergeCell ref="C77:C81"/>
-    <mergeCell ref="D77:D81"/>
-    <mergeCell ref="E77:E81"/>
-    <mergeCell ref="A62:A66"/>
-    <mergeCell ref="B62:B66"/>
-    <mergeCell ref="C62:C66"/>
-    <mergeCell ref="D62:D66"/>
-    <mergeCell ref="E62:E66"/>
-    <mergeCell ref="A67:A71"/>
-    <mergeCell ref="B67:B71"/>
-    <mergeCell ref="C67:C71"/>
-    <mergeCell ref="D67:D71"/>
-    <mergeCell ref="E67:E71"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="B52:B56"/>
-    <mergeCell ref="C52:C56"/>
-    <mergeCell ref="D52:D56"/>
-    <mergeCell ref="E52:E56"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="C57:C61"/>
-    <mergeCell ref="D57:D61"/>
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="A42:A46"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="C42:C46"/>
-    <mergeCell ref="D42:D46"/>
-    <mergeCell ref="E42:E46"/>
-    <mergeCell ref="A47:A51"/>
-    <mergeCell ref="B47:B51"/>
-    <mergeCell ref="C47:C51"/>
-    <mergeCell ref="D47:D51"/>
-    <mergeCell ref="E47:E51"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="C32:C36"/>
-    <mergeCell ref="D32:D36"/>
-    <mergeCell ref="E32:E36"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B22:B26"/>
-    <mergeCell ref="C22:C26"/>
-    <mergeCell ref="D22:D26"/>
-    <mergeCell ref="E22:E26"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="C27:C31"/>
-    <mergeCell ref="D27:D31"/>
-    <mergeCell ref="E27:E31"/>
-    <mergeCell ref="A12:A16"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="E12:E16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="C17:C21"/>
-    <mergeCell ref="D17:D21"/>
-    <mergeCell ref="E17:E21"/>
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="B2:B6"/>
-    <mergeCell ref="C2:C6"/>
-    <mergeCell ref="D2:D6"/>
-    <mergeCell ref="E2:E6"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="E7:E11"/>
   </mergeCells>
   <conditionalFormatting sqref="I2:I151">
     <cfRule type="dataBar" priority="3">
@@ -17920,13 +17984,13 @@
     <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Fecha inválida" error="Ingresa una fecha válida (DD/MM/AAAA)." sqref="G2:G151" xr:uid="{91BC26E3-EEE8-449B-863E-945CFEC2CF49}">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I155:I184 K2:K151" xr:uid="{4AE3507A-C182-4E5D-ADBD-341010D3A3DE}">
+    <dataValidation type="list" allowBlank="1" sqref="I155:I184 K2 K7 K12 K17 K22 K27 K32 K37 K42 K47 K52 K57 K62 K67 K72 K77 K82 K87 K92 K97 K102 K107 K112 K117 K122 K127 K132 K137 K142 K147" xr:uid="{4AE3507A-C182-4E5D-ADBD-341010D3A3DE}">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F2:F151" xr:uid="{7D9B4586-77AF-4A2D-BE33-305B91F90513}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Valor fuera de rango" error="La actitud se califica de 1 a 5." sqref="J2:K2 J4:J151 K3:K151" xr:uid="{6BD76E45-46DD-419C-A5D0-52A84DA3D8AC}">
+    <dataValidation type="whole" allowBlank="1" showErrorMessage="1" errorTitle="Valor fuera de rango" error="La actitud se califica de 1 a 5." sqref="J2:K2 J4:J151 K7 K12 K17 K22 K27 K32 K37 K42 K47 K52 K57 K62 K67 K72 K77 K82 K87 K92 K97 K102 K107 K112 K117 K122 K127 K132 K137 K142 K147" xr:uid="{6BD76E45-46DD-419C-A5D0-52A84DA3D8AC}">
       <formula1>1</formula1>
       <formula2>5</formula2>
     </dataValidation>
@@ -18196,12 +18260,12 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="17.25">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="108" t="s">
         <v>97</v>
       </c>
-      <c r="B28" s="100"/>
-      <c r="C28" s="100"/>
-      <c r="D28" s="100"/>
+      <c r="B28" s="108"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="32" t="s">
